--- a/Mapathon/outputs/tables/cmrl_data.xlsx
+++ b/Mapathon/outputs/tables/cmrl_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46257</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20788</v>
+        <v>164932</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
@@ -493,20 +493,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46256</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>306203</v>
+        <v>379454</v>
       </c>
       <c r="E3" t="n">
         <v>41</v>
@@ -514,11 +514,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46255</v>
+        <v>46266</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>372199</v>
+        <v>377033</v>
       </c>
       <c r="E4" t="n">
         <v>41</v>
@@ -535,11 +535,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>377617</v>
+        <v>375609</v>
       </c>
       <c r="E5" t="n">
         <v>41</v>
@@ -556,20 +556,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46253</v>
+        <v>46264</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>381888</v>
+        <v>206719</v>
       </c>
       <c r="E6" t="n">
         <v>41</v>
@@ -577,20 +577,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46252</v>
+        <v>46263</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>379824</v>
+        <v>315226</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -598,11 +598,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46251</v>
+        <v>46262</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>376881</v>
+        <v>368873</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
@@ -619,22 +619,253 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>372194</v>
+      </c>
+      <c r="E9" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>295293</v>
+      </c>
+      <c r="E10" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>379448</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>378136</v>
+      </c>
+      <c r="E12" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>217114</v>
+      </c>
+      <c r="E13" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>306203</v>
+      </c>
+      <c r="E14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>372199</v>
+      </c>
+      <c r="E15" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>377617</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>381888</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>379824</v>
+      </c>
+      <c r="E18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>376881</v>
+      </c>
+      <c r="E19" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
         <v>46250</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>weekend</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D20" t="n">
         <v>192613</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E20" t="n">
         <v>41</v>
       </c>
     </row>
@@ -649,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -661,6 +892,17 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -709,6 +951,61 @@
           <t>2026-08-22 Sat</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 Sun</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-24 Mon</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-25 Tue</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-26 Wed</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 Thu</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 Fri</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 Sat</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 Sun</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 Mon</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01 Tue</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02 Wed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -717,7 +1014,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31592</v>
+        <v>31316</v>
       </c>
       <c r="C2" t="n">
         <v>20610</v>
@@ -740,67 +1037,166 @@
       <c r="I2" t="n">
         <v>28062</v>
       </c>
+      <c r="J2" t="n">
+        <v>22585</v>
+      </c>
+      <c r="K2" t="n">
+        <v>33388</v>
+      </c>
+      <c r="L2" t="n">
+        <v>31278</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25752</v>
+      </c>
+      <c r="N2" t="n">
+        <v>31151</v>
+      </c>
+      <c r="O2" t="n">
+        <v>31175</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28803</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>21926</v>
+      </c>
+      <c r="R2" t="n">
+        <v>33348</v>
+      </c>
+      <c r="S2" t="n">
+        <v>31357</v>
+      </c>
+      <c r="T2" t="n">
+        <v>31706</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHENNAI AIRPORT</t>
+          <t>THOUSAND LIGHT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19584</v>
+        <v>18694</v>
       </c>
       <c r="C3" t="n">
-        <v>15071</v>
+        <v>5047</v>
       </c>
       <c r="D3" t="n">
-        <v>19893</v>
+        <v>19138</v>
       </c>
       <c r="E3" t="n">
-        <v>19042</v>
+        <v>19507</v>
       </c>
       <c r="F3" t="n">
-        <v>19230</v>
+        <v>19692</v>
       </c>
       <c r="G3" t="n">
-        <v>19110</v>
+        <v>19501</v>
       </c>
       <c r="H3" t="n">
-        <v>20647</v>
+        <v>18896</v>
       </c>
       <c r="I3" t="n">
-        <v>19081</v>
+        <v>11033</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5005</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18987</v>
+      </c>
+      <c r="L3" t="n">
+        <v>19510</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13740</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18617</v>
+      </c>
+      <c r="O3" t="n">
+        <v>18322</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13264</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5586</v>
+      </c>
+      <c r="R3" t="n">
+        <v>18616</v>
+      </c>
+      <c r="S3" t="n">
+        <v>19033</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VADAPALANI</t>
+          <t>CHENNAI AIRPORT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13794</v>
+        <v>19134</v>
       </c>
       <c r="C4" t="n">
-        <v>10793</v>
+        <v>15071</v>
       </c>
       <c r="D4" t="n">
-        <v>13040</v>
+        <v>19893</v>
       </c>
       <c r="E4" t="n">
-        <v>14945</v>
+        <v>19042</v>
       </c>
       <c r="F4" t="n">
-        <v>13565</v>
+        <v>19230</v>
       </c>
       <c r="G4" t="n">
-        <v>13254</v>
+        <v>19110</v>
       </c>
       <c r="H4" t="n">
-        <v>14164</v>
+        <v>20647</v>
       </c>
       <c r="I4" t="n">
-        <v>14745</v>
+        <v>19081</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15971</v>
+      </c>
+      <c r="K4" t="n">
+        <v>19113</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18883</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17288</v>
+      </c>
+      <c r="N4" t="n">
+        <v>19033</v>
+      </c>
+      <c r="O4" t="n">
+        <v>19531</v>
+      </c>
+      <c r="P4" t="n">
+        <v>18898</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15462</v>
+      </c>
+      <c r="R4" t="n">
+        <v>19180</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18900</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18898</v>
       </c>
     </row>
     <row r="5">
@@ -810,7 +1206,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17412</v>
+        <v>17151</v>
       </c>
       <c r="C5" t="n">
         <v>9140</v>
@@ -833,6 +1229,39 @@
       <c r="I5" t="n">
         <v>14152</v>
       </c>
+      <c r="J5" t="n">
+        <v>10334</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17190</v>
+      </c>
+      <c r="L5" t="n">
+        <v>17611</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14529</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17019</v>
+      </c>
+      <c r="O5" t="n">
+        <v>17265</v>
+      </c>
+      <c r="P5" t="n">
+        <v>14632</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10024</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17019</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17627</v>
+      </c>
+      <c r="T5" t="n">
+        <v>17648</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -841,7 +1270,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17470</v>
+        <v>16986</v>
       </c>
       <c r="C6" t="n">
         <v>8360</v>
@@ -864,6 +1293,39 @@
       <c r="I6" t="n">
         <v>13472</v>
       </c>
+      <c r="J6" t="n">
+        <v>9649</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17223</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17309</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13844</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16913</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17140</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14631</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>17025</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16705</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17305</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -872,7 +1334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13838</v>
+        <v>13786</v>
       </c>
       <c r="C7" t="n">
         <v>9042</v>
@@ -895,749 +1357,1574 @@
       <c r="I7" t="n">
         <v>12584</v>
       </c>
+      <c r="J7" t="n">
+        <v>9931</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14743</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14252</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10957</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13693</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13638</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11896</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9149</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14557</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14108</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14084</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THOUSAND LIGHT</t>
+          <t>HIGH COURT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19347</v>
+        <v>13544</v>
       </c>
       <c r="C8" t="n">
-        <v>5047</v>
+        <v>3599</v>
       </c>
       <c r="D8" t="n">
-        <v>19138</v>
+        <v>13539</v>
       </c>
       <c r="E8" t="n">
-        <v>19507</v>
+        <v>14815</v>
       </c>
       <c r="F8" t="n">
-        <v>19692</v>
+        <v>14124</v>
       </c>
       <c r="G8" t="n">
-        <v>19501</v>
+        <v>13588</v>
       </c>
       <c r="H8" t="n">
-        <v>18896</v>
+        <v>12854</v>
       </c>
       <c r="I8" t="n">
-        <v>11033</v>
+        <v>9406</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4305</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13885</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14290</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7338</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17218</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12784</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9909</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3595</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13042</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14945</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13650</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALANDUR</t>
+          <t>VADAPALANI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13224</v>
+        <v>13712</v>
       </c>
       <c r="C9" t="n">
-        <v>6875</v>
+        <v>10793</v>
       </c>
       <c r="D9" t="n">
-        <v>12980</v>
+        <v>13040</v>
       </c>
       <c r="E9" t="n">
-        <v>13355</v>
+        <v>14945</v>
       </c>
       <c r="F9" t="n">
-        <v>13488</v>
+        <v>13565</v>
       </c>
       <c r="G9" t="n">
-        <v>13140</v>
+        <v>13254</v>
       </c>
       <c r="H9" t="n">
-        <v>13155</v>
+        <v>14164</v>
       </c>
       <c r="I9" t="n">
-        <v>11014</v>
+        <v>14745</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12846</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12906</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14423</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13576</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13305</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13879</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14218</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>13265</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14557</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13374</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOVERNMENT ESTATE</t>
+          <t>ALANDUR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10870</v>
+        <v>12841</v>
       </c>
       <c r="C10" t="n">
-        <v>5081</v>
+        <v>6875</v>
       </c>
       <c r="D10" t="n">
-        <v>10634</v>
+        <v>12980</v>
       </c>
       <c r="E10" t="n">
-        <v>11172</v>
+        <v>13355</v>
       </c>
       <c r="F10" t="n">
-        <v>11076</v>
+        <v>13488</v>
       </c>
       <c r="G10" t="n">
-        <v>10903</v>
+        <v>13140</v>
       </c>
       <c r="H10" t="n">
-        <v>10567</v>
+        <v>13155</v>
       </c>
       <c r="I10" t="n">
-        <v>9948</v>
+        <v>11014</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7839</v>
+      </c>
+      <c r="K10" t="n">
+        <v>12821</v>
+      </c>
+      <c r="L10" t="n">
+        <v>13074</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11035</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12312</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12687</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11443</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7599</v>
+      </c>
+      <c r="R10" t="n">
+        <v>12769</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13050</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HIGH COURT</t>
+          <t>LIC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13784</v>
+        <v>11291</v>
       </c>
       <c r="C11" t="n">
-        <v>3599</v>
+        <v>3680</v>
       </c>
       <c r="D11" t="n">
-        <v>13539</v>
+        <v>11469</v>
       </c>
       <c r="E11" t="n">
-        <v>14815</v>
+        <v>11774</v>
       </c>
       <c r="F11" t="n">
-        <v>14124</v>
+        <v>11846</v>
       </c>
       <c r="G11" t="n">
-        <v>13588</v>
+        <v>11878</v>
       </c>
       <c r="H11" t="n">
-        <v>12854</v>
+        <v>10307</v>
       </c>
       <c r="I11" t="n">
-        <v>9406</v>
+        <v>6144</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3657</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11713</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11971</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7550</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11624</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11418</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7132</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3620</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11272</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11838</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASHOK NAGAR</t>
+          <t>TEYNAMPET</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9871</v>
+        <v>10580</v>
       </c>
       <c r="C12" t="n">
-        <v>4372</v>
+        <v>2852</v>
       </c>
       <c r="D12" t="n">
-        <v>9905</v>
+        <v>10642</v>
       </c>
       <c r="E12" t="n">
-        <v>9740</v>
+        <v>10992</v>
       </c>
       <c r="F12" t="n">
-        <v>10037</v>
+        <v>11036</v>
       </c>
       <c r="G12" t="n">
-        <v>9754</v>
+        <v>10957</v>
       </c>
       <c r="H12" t="n">
-        <v>9921</v>
+        <v>10783</v>
       </c>
       <c r="I12" t="n">
-        <v>8948</v>
+        <v>6792</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2889</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10901</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10854</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7659</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10754</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10759</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8192</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2976</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10442</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10794</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10964</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>St. THOMAS MOUNT</t>
+          <t>GOVERNMENT ESTATE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8829</v>
+        <v>10696</v>
       </c>
       <c r="C13" t="n">
-        <v>5212</v>
+        <v>5081</v>
       </c>
       <c r="D13" t="n">
-        <v>8518</v>
+        <v>10634</v>
       </c>
       <c r="E13" t="n">
-        <v>8966</v>
+        <v>11172</v>
       </c>
       <c r="F13" t="n">
-        <v>8853</v>
+        <v>11076</v>
       </c>
       <c r="G13" t="n">
-        <v>8926</v>
+        <v>10903</v>
       </c>
       <c r="H13" t="n">
-        <v>8883</v>
+        <v>10567</v>
       </c>
       <c r="I13" t="n">
-        <v>7919</v>
+        <v>9948</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5610</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10635</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10855</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8733</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10912</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11587</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9284</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5002</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10684</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10499</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>EKKATTUTHANGAL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7894</v>
+        <v>9528</v>
       </c>
       <c r="C14" t="n">
-        <v>5729</v>
+        <v>2842</v>
       </c>
       <c r="D14" t="n">
-        <v>8269</v>
+        <v>9115</v>
       </c>
       <c r="E14" t="n">
-        <v>7884</v>
+        <v>9966</v>
       </c>
       <c r="F14" t="n">
-        <v>7720</v>
+        <v>10233</v>
       </c>
       <c r="G14" t="n">
-        <v>7541</v>
+        <v>9927</v>
       </c>
       <c r="H14" t="n">
-        <v>8054</v>
+        <v>9562</v>
       </c>
       <c r="I14" t="n">
-        <v>7847</v>
+        <v>5453</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3205</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9154</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9768</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8431</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9345</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9234</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5503</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3135</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9293</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9796</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEYNAMPET</t>
+          <t>ASHOK NAGAR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10882</v>
+        <v>9566</v>
       </c>
       <c r="C15" t="n">
-        <v>2852</v>
+        <v>4372</v>
       </c>
       <c r="D15" t="n">
-        <v>10642</v>
+        <v>9905</v>
       </c>
       <c r="E15" t="n">
-        <v>10992</v>
+        <v>9740</v>
       </c>
       <c r="F15" t="n">
-        <v>11036</v>
+        <v>10037</v>
       </c>
       <c r="G15" t="n">
-        <v>10957</v>
+        <v>9754</v>
       </c>
       <c r="H15" t="n">
-        <v>10783</v>
+        <v>9921</v>
       </c>
       <c r="I15" t="n">
-        <v>6792</v>
+        <v>8948</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5124</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10057</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10340</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7094</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8605</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9599</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7983</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5011</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9788</v>
+      </c>
+      <c r="T15" t="n">
+        <v>9870</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MEENAMBAKKAM</t>
+          <t>AG-DMS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7676</v>
+        <v>8977</v>
       </c>
       <c r="C16" t="n">
-        <v>4033</v>
+        <v>2324</v>
       </c>
       <c r="D16" t="n">
-        <v>7855</v>
+        <v>9167</v>
       </c>
       <c r="E16" t="n">
-        <v>7631</v>
+        <v>9586</v>
       </c>
       <c r="F16" t="n">
-        <v>7777</v>
+        <v>9582</v>
       </c>
       <c r="G16" t="n">
-        <v>7746</v>
+        <v>10111</v>
       </c>
       <c r="H16" t="n">
-        <v>7371</v>
+        <v>9722</v>
       </c>
       <c r="I16" t="n">
-        <v>6771</v>
+        <v>5668</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2442</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9028</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9177</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5508</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8980</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8784</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5515</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2536</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8935</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8899</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WASHERMANPET</t>
+          <t>St. THOMAS MOUNT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8453</v>
+        <v>8673</v>
       </c>
       <c r="C17" t="n">
-        <v>4003</v>
+        <v>5212</v>
       </c>
       <c r="D17" t="n">
-        <v>8476</v>
+        <v>8518</v>
       </c>
       <c r="E17" t="n">
-        <v>8491</v>
+        <v>8966</v>
       </c>
       <c r="F17" t="n">
-        <v>8595</v>
+        <v>8853</v>
       </c>
       <c r="G17" t="n">
-        <v>8636</v>
+        <v>8926</v>
       </c>
       <c r="H17" t="n">
-        <v>8069</v>
+        <v>8883</v>
       </c>
       <c r="I17" t="n">
-        <v>6477</v>
+        <v>7919</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8815</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9041</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7501</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8395</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8449</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7794</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5501</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8707</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9034</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THIYAGARAYA COLLEGE METRO</t>
+          <t>WASHERMANPET</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7220</v>
+        <v>8262</v>
       </c>
       <c r="C18" t="n">
-        <v>4309</v>
+        <v>4003</v>
       </c>
       <c r="D18" t="n">
-        <v>7263</v>
+        <v>8476</v>
       </c>
       <c r="E18" t="n">
-        <v>7166</v>
+        <v>8491</v>
       </c>
       <c r="F18" t="n">
-        <v>7273</v>
+        <v>8595</v>
       </c>
       <c r="G18" t="n">
-        <v>7417</v>
+        <v>8636</v>
       </c>
       <c r="H18" t="n">
-        <v>6980</v>
+        <v>8069</v>
       </c>
       <c r="I18" t="n">
-        <v>6253</v>
+        <v>6477</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4493</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8345</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8485</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6228</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8309</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8223</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6570</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4298</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8462</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8458</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THIRUVOTRIYUR THERADI METRO</t>
+          <t>NANDANAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6248</v>
+        <v>8076</v>
       </c>
       <c r="C19" t="n">
-        <v>4224</v>
+        <v>2019</v>
       </c>
       <c r="D19" t="n">
-        <v>6165</v>
+        <v>7958</v>
       </c>
       <c r="E19" t="n">
-        <v>6222</v>
+        <v>8410</v>
       </c>
       <c r="F19" t="n">
-        <v>6129</v>
+        <v>8460</v>
       </c>
       <c r="G19" t="n">
-        <v>6332</v>
+        <v>8434</v>
       </c>
       <c r="H19" t="n">
-        <v>6393</v>
+        <v>8389</v>
       </c>
       <c r="I19" t="n">
-        <v>6163</v>
+        <v>4552</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2247</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8159</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8542</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5839</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8108</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8038</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6463</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2108</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7985</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8238</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8426</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>LITTLE MOUNT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11455</v>
+        <v>7665</v>
       </c>
       <c r="C20" t="n">
-        <v>3680</v>
+        <v>3363</v>
       </c>
       <c r="D20" t="n">
-        <v>11469</v>
+        <v>7386</v>
       </c>
       <c r="E20" t="n">
-        <v>11774</v>
+        <v>7725</v>
       </c>
       <c r="F20" t="n">
-        <v>11846</v>
+        <v>8126</v>
       </c>
       <c r="G20" t="n">
-        <v>11878</v>
+        <v>7874</v>
       </c>
       <c r="H20" t="n">
-        <v>10307</v>
+        <v>8085</v>
       </c>
       <c r="I20" t="n">
-        <v>6144</v>
+        <v>5171</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3931</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7690</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7922</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6357</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7756</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6331</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3585</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7338</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7657</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8009</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TONDIARPET METRO</t>
+          <t>SAIDAPET</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7020</v>
+        <v>7372</v>
       </c>
       <c r="C21" t="n">
-        <v>3718</v>
+        <v>3326</v>
       </c>
       <c r="D21" t="n">
-        <v>7017</v>
+        <v>7667</v>
       </c>
       <c r="E21" t="n">
-        <v>7052</v>
+        <v>7656</v>
       </c>
       <c r="F21" t="n">
-        <v>7203</v>
+        <v>7918</v>
       </c>
       <c r="G21" t="n">
-        <v>7093</v>
+        <v>7722</v>
       </c>
       <c r="H21" t="n">
-        <v>6735</v>
+        <v>7303</v>
       </c>
       <c r="I21" t="n">
-        <v>6139</v>
+        <v>4748</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3331</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7779</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7675</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4505</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7515</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7231</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5066</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3095</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7343</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7649</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7874</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANNA NAGAR EAST</t>
+          <t>MEENAMBAKKAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7248</v>
+        <v>7416</v>
       </c>
       <c r="C22" t="n">
-        <v>3712</v>
+        <v>4033</v>
       </c>
       <c r="D22" t="n">
-        <v>7377</v>
+        <v>7855</v>
       </c>
       <c r="E22" t="n">
-        <v>7373</v>
+        <v>7631</v>
       </c>
       <c r="F22" t="n">
-        <v>7471</v>
+        <v>7777</v>
       </c>
       <c r="G22" t="n">
-        <v>7394</v>
+        <v>7746</v>
       </c>
       <c r="H22" t="n">
-        <v>6627</v>
+        <v>7371</v>
       </c>
       <c r="I22" t="n">
-        <v>5956</v>
+        <v>6771</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4767</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7853</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7526</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5227</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7287</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6643</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6093</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4538</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8060</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7700</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7731</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EGMORE</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5757</v>
+        <v>7793</v>
       </c>
       <c r="C23" t="n">
-        <v>4506</v>
+        <v>5729</v>
       </c>
       <c r="D23" t="n">
-        <v>6004</v>
+        <v>8269</v>
       </c>
       <c r="E23" t="n">
-        <v>5612</v>
+        <v>7884</v>
       </c>
       <c r="F23" t="n">
-        <v>5795</v>
+        <v>7720</v>
       </c>
       <c r="G23" t="n">
-        <v>5521</v>
+        <v>7541</v>
       </c>
       <c r="H23" t="n">
-        <v>5855</v>
+        <v>8054</v>
       </c>
       <c r="I23" t="n">
-        <v>5887</v>
+        <v>7847</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6459</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8457</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7747</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6642</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7632</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7795</v>
+      </c>
+      <c r="P23" t="n">
+        <v>7097</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6083</v>
+      </c>
+      <c r="R23" t="n">
+        <v>8277</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7753</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ANNA NAGAR TOWER</t>
+          <t>THIYAGARAYA COLLEGE METRO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6556</v>
+        <v>7122</v>
       </c>
       <c r="C24" t="n">
-        <v>3679</v>
+        <v>4309</v>
       </c>
       <c r="D24" t="n">
-        <v>6366</v>
+        <v>7263</v>
       </c>
       <c r="E24" t="n">
-        <v>6571</v>
+        <v>7166</v>
       </c>
       <c r="F24" t="n">
-        <v>6775</v>
+        <v>7273</v>
       </c>
       <c r="G24" t="n">
-        <v>6937</v>
+        <v>7417</v>
       </c>
       <c r="H24" t="n">
-        <v>6129</v>
+        <v>6980</v>
       </c>
       <c r="I24" t="n">
-        <v>5839</v>
+        <v>6253</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5102</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7306</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7308</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5579</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7317</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7071</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6403</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4725</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>7075</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7340</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MANNADI</t>
+          <t>ANNA NAGAR EAST</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7026</v>
+        <v>7154</v>
       </c>
       <c r="C25" t="n">
-        <v>3456</v>
+        <v>3712</v>
       </c>
       <c r="D25" t="n">
-        <v>6880</v>
+        <v>7377</v>
       </c>
       <c r="E25" t="n">
-        <v>7207</v>
+        <v>7373</v>
       </c>
       <c r="F25" t="n">
-        <v>7182</v>
+        <v>7471</v>
       </c>
       <c r="G25" t="n">
-        <v>7153</v>
+        <v>7394</v>
       </c>
       <c r="H25" t="n">
-        <v>6707</v>
+        <v>6627</v>
       </c>
       <c r="I25" t="n">
-        <v>5717</v>
+        <v>5956</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4327</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7230</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7311</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5909</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7247</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7195</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6318</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3889</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7290</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7290</v>
+      </c>
+      <c r="T25" t="n">
+        <v>7282</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AG-DMS</t>
+          <t>MANNADI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9634</v>
+        <v>6836</v>
       </c>
       <c r="C26" t="n">
-        <v>2324</v>
+        <v>3456</v>
       </c>
       <c r="D26" t="n">
-        <v>9167</v>
+        <v>6880</v>
       </c>
       <c r="E26" t="n">
-        <v>9586</v>
+        <v>7207</v>
       </c>
       <c r="F26" t="n">
-        <v>9582</v>
+        <v>7182</v>
       </c>
       <c r="G26" t="n">
-        <v>10111</v>
+        <v>7153</v>
       </c>
       <c r="H26" t="n">
-        <v>9722</v>
+        <v>6707</v>
       </c>
       <c r="I26" t="n">
-        <v>5668</v>
+        <v>5717</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3630</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6960</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6953</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5284</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6610</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6823</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6099</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3646</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6945</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6983</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7179</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EKKATTUTHANGAL</t>
+          <t>TONDIARPET METRO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9761</v>
+        <v>6936</v>
       </c>
       <c r="C27" t="n">
-        <v>2842</v>
+        <v>3718</v>
       </c>
       <c r="D27" t="n">
-        <v>9115</v>
+        <v>7017</v>
       </c>
       <c r="E27" t="n">
-        <v>9966</v>
+        <v>7052</v>
       </c>
       <c r="F27" t="n">
-        <v>10233</v>
+        <v>7203</v>
       </c>
       <c r="G27" t="n">
-        <v>9927</v>
+        <v>7093</v>
       </c>
       <c r="H27" t="n">
-        <v>9562</v>
+        <v>6735</v>
       </c>
       <c r="I27" t="n">
-        <v>5453</v>
+        <v>6139</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4676</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7079</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7101</v>
+      </c>
+      <c r="M27" t="n">
+        <v>5643</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7036</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6939</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5959</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7280</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6937</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7058</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LITTLE MOUNT</t>
+          <t>ANNA NAGAR TOWER</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7839</v>
+        <v>6433</v>
       </c>
       <c r="C28" t="n">
-        <v>3363</v>
+        <v>3679</v>
       </c>
       <c r="D28" t="n">
-        <v>7386</v>
+        <v>6366</v>
       </c>
       <c r="E28" t="n">
-        <v>7725</v>
+        <v>6571</v>
       </c>
       <c r="F28" t="n">
-        <v>8126</v>
+        <v>6775</v>
       </c>
       <c r="G28" t="n">
-        <v>7874</v>
+        <v>6937</v>
       </c>
       <c r="H28" t="n">
-        <v>8085</v>
+        <v>6129</v>
       </c>
       <c r="I28" t="n">
-        <v>5171</v>
+        <v>5839</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3755</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6339</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6548</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5379</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6505</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6366</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6178</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3905</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6521</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6504</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6691</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WIMCO NAGAR METRO</t>
+          <t>THIRUVOTRIYUR THERADI METRO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5847</v>
+        <v>6231</v>
       </c>
       <c r="C29" t="n">
-        <v>2965</v>
+        <v>4224</v>
       </c>
       <c r="D29" t="n">
-        <v>6042</v>
+        <v>6165</v>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>6222</v>
       </c>
       <c r="F29" t="n">
-        <v>5902</v>
+        <v>6129</v>
       </c>
       <c r="G29" t="n">
-        <v>5827</v>
+        <v>6332</v>
       </c>
       <c r="H29" t="n">
-        <v>5717</v>
+        <v>6393</v>
       </c>
       <c r="I29" t="n">
-        <v>5073</v>
+        <v>6163</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5396</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6235</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6360</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5283</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6515</v>
+      </c>
+      <c r="O29" t="n">
+        <v>6358</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5852</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5132</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6614</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6210</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6192</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ARUMBAKKAM</t>
+          <t>EGMORE</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5328</v>
+        <v>5761</v>
       </c>
       <c r="C30" t="n">
-        <v>2952</v>
+        <v>4506</v>
       </c>
       <c r="D30" t="n">
-        <v>5072</v>
+        <v>6004</v>
       </c>
       <c r="E30" t="n">
-        <v>5229</v>
+        <v>5612</v>
       </c>
       <c r="F30" t="n">
-        <v>5474</v>
+        <v>5795</v>
       </c>
       <c r="G30" t="n">
-        <v>5294</v>
+        <v>5521</v>
       </c>
       <c r="H30" t="n">
-        <v>5569</v>
+        <v>5855</v>
       </c>
       <c r="I30" t="n">
-        <v>5066</v>
+        <v>5887</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4644</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5958</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5586</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5042</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5727</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5727</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5600</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4886</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6169</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6028</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5873</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KALADIPET METRO</t>
+          <t>WIMCO NAGAR METRO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5446</v>
+        <v>5760</v>
       </c>
       <c r="C31" t="n">
-        <v>3260</v>
+        <v>2965</v>
       </c>
       <c r="D31" t="n">
-        <v>5512</v>
+        <v>6042</v>
       </c>
       <c r="E31" t="n">
-        <v>5397</v>
+        <v>5747</v>
       </c>
       <c r="F31" t="n">
-        <v>5522</v>
+        <v>5902</v>
       </c>
       <c r="G31" t="n">
-        <v>5472</v>
+        <v>5827</v>
       </c>
       <c r="H31" t="n">
-        <v>5327</v>
+        <v>5717</v>
       </c>
       <c r="I31" t="n">
-        <v>4889</v>
+        <v>5073</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3349</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5954</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5917</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4645</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5758</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5899</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5118</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3303</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5915</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5721</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5836</v>
       </c>
     </row>
     <row r="32">
@@ -1647,7 +2934,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5637</v>
+        <v>5572</v>
       </c>
       <c r="C32" t="n">
         <v>3183</v>
@@ -1670,129 +2957,294 @@
       <c r="I32" t="n">
         <v>4765</v>
       </c>
+      <c r="J32" t="n">
+        <v>3818</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5737</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5714</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4573</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5708</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5579</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4826</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3254</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5537</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5687</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5714</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAIDAPET</t>
+          <t>KALADIPET METRO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7653</v>
+        <v>5380</v>
       </c>
       <c r="C33" t="n">
-        <v>3326</v>
+        <v>3260</v>
       </c>
       <c r="D33" t="n">
-        <v>7667</v>
+        <v>5512</v>
       </c>
       <c r="E33" t="n">
-        <v>7656</v>
+        <v>5397</v>
       </c>
       <c r="F33" t="n">
-        <v>7918</v>
+        <v>5522</v>
       </c>
       <c r="G33" t="n">
-        <v>7722</v>
+        <v>5472</v>
       </c>
       <c r="H33" t="n">
-        <v>7303</v>
+        <v>5327</v>
       </c>
       <c r="I33" t="n">
-        <v>4748</v>
+        <v>4889</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3959</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5471</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5373</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4267</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5443</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5373</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4864</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3384</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5666</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5489</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5634</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NANDANAM</t>
+          <t>ARUMBAKKAM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8330</v>
+        <v>5274</v>
       </c>
       <c r="C34" t="n">
-        <v>2019</v>
+        <v>2952</v>
       </c>
       <c r="D34" t="n">
-        <v>7958</v>
+        <v>5072</v>
       </c>
       <c r="E34" t="n">
-        <v>8410</v>
+        <v>5229</v>
       </c>
       <c r="F34" t="n">
-        <v>8460</v>
+        <v>5474</v>
       </c>
       <c r="G34" t="n">
-        <v>8434</v>
+        <v>5294</v>
       </c>
       <c r="H34" t="n">
-        <v>8389</v>
+        <v>5569</v>
       </c>
       <c r="I34" t="n">
-        <v>4552</v>
+        <v>5066</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3710</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5257</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5345</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5074</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5132</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5064</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4873</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3361</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5197</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5468</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5390</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NEW WASHERMENPET METRO</t>
+          <t>THIRUVOTRIYUR METRO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5196</v>
+        <v>4912</v>
       </c>
       <c r="C35" t="n">
-        <v>2783</v>
+        <v>3087</v>
       </c>
       <c r="D35" t="n">
-        <v>5198</v>
+        <v>5015</v>
       </c>
       <c r="E35" t="n">
-        <v>5282</v>
+        <v>5086</v>
       </c>
       <c r="F35" t="n">
-        <v>5346</v>
+        <v>5029</v>
       </c>
       <c r="G35" t="n">
-        <v>5093</v>
+        <v>4866</v>
       </c>
       <c r="H35" t="n">
-        <v>5059</v>
+        <v>4663</v>
       </c>
       <c r="I35" t="n">
-        <v>4387</v>
+        <v>4269</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3645</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5158</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4915</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4016</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4863</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5084</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4797</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3386</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5129</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4919</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5114</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>THIRUVOTRIYUR METRO</t>
+          <t>NEW WASHERMENPET METRO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4932</v>
+        <v>5045</v>
       </c>
       <c r="C36" t="n">
-        <v>3087</v>
+        <v>2783</v>
       </c>
       <c r="D36" t="n">
-        <v>5015</v>
+        <v>5198</v>
       </c>
       <c r="E36" t="n">
-        <v>5086</v>
+        <v>5282</v>
       </c>
       <c r="F36" t="n">
-        <v>5029</v>
+        <v>5346</v>
       </c>
       <c r="G36" t="n">
-        <v>4866</v>
+        <v>5093</v>
       </c>
       <c r="H36" t="n">
-        <v>4663</v>
+        <v>5059</v>
       </c>
       <c r="I36" t="n">
-        <v>4269</v>
+        <v>4387</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3409</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5173</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5104</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3970</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4892</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4951</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4333</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3206</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5419</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5012</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5089</v>
       </c>
     </row>
     <row r="37">
@@ -1802,7 +3254,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3742</v>
+        <v>3692</v>
       </c>
       <c r="C37" t="n">
         <v>1898</v>
@@ -1825,160 +3277,358 @@
       <c r="I37" t="n">
         <v>3143</v>
       </c>
+      <c r="J37" t="n">
+        <v>2351</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3766</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3795</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2994</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3580</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3591</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3259</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2082</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3736</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3876</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3943</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NEHRU PARK</t>
+          <t>PACHAIAPPA S COLLEGE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3197</v>
+        <v>3299</v>
       </c>
       <c r="C38" t="n">
-        <v>1872</v>
+        <v>1418</v>
       </c>
       <c r="D38" t="n">
-        <v>3109</v>
+        <v>3438</v>
       </c>
       <c r="E38" t="n">
-        <v>3079</v>
+        <v>3407</v>
       </c>
       <c r="F38" t="n">
-        <v>3162</v>
+        <v>3402</v>
       </c>
       <c r="G38" t="n">
-        <v>3400</v>
+        <v>3366</v>
       </c>
       <c r="H38" t="n">
-        <v>3234</v>
+        <v>2815</v>
       </c>
       <c r="I38" t="n">
-        <v>3082</v>
+        <v>2551</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1724</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3362</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3323</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2348</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3580</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3313</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3306</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1653</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3428</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3503</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3604</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PACHAIAPPA S COLLEGE</t>
+          <t>NEHRU PARK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3286</v>
+        <v>3116</v>
       </c>
       <c r="C39" t="n">
-        <v>1418</v>
+        <v>1872</v>
       </c>
       <c r="D39" t="n">
-        <v>3438</v>
+        <v>3109</v>
       </c>
       <c r="E39" t="n">
-        <v>3407</v>
+        <v>3079</v>
       </c>
       <c r="F39" t="n">
-        <v>3402</v>
+        <v>3162</v>
       </c>
       <c r="G39" t="n">
-        <v>3366</v>
+        <v>3400</v>
       </c>
       <c r="H39" t="n">
-        <v>2815</v>
+        <v>3234</v>
       </c>
       <c r="I39" t="n">
-        <v>2551</v>
+        <v>3082</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2176</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3259</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3164</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2702</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2933</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3041</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3105</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1931</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3038</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3051</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3330</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KILPAUK</t>
+          <t>OTA - NANGANALLUR ROAD</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2963</v>
+        <v>3118</v>
       </c>
       <c r="C40" t="n">
-        <v>1294</v>
+        <v>1095</v>
       </c>
       <c r="D40" t="n">
-        <v>2961</v>
+        <v>3091</v>
       </c>
       <c r="E40" t="n">
-        <v>2947</v>
+        <v>3162</v>
       </c>
       <c r="F40" t="n">
-        <v>3016</v>
+        <v>3204</v>
       </c>
       <c r="G40" t="n">
-        <v>3030</v>
+        <v>3270</v>
       </c>
       <c r="H40" t="n">
-        <v>2860</v>
+        <v>2999</v>
       </c>
       <c r="I40" t="n">
-        <v>2535</v>
+        <v>2119</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1363</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3213</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3236</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2313</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3130</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3136</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2489</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1299</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3154</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3309</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3321</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TOLLGATE METRO</t>
+          <t>KILPAUK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2698</v>
+        <v>2912</v>
       </c>
       <c r="C41" t="n">
-        <v>1829</v>
+        <v>1294</v>
       </c>
       <c r="D41" t="n">
-        <v>2698</v>
+        <v>2961</v>
       </c>
       <c r="E41" t="n">
-        <v>2679</v>
+        <v>2947</v>
       </c>
       <c r="F41" t="n">
-        <v>2919</v>
+        <v>3016</v>
       </c>
       <c r="G41" t="n">
-        <v>2684</v>
+        <v>3030</v>
       </c>
       <c r="H41" t="n">
-        <v>2510</v>
+        <v>2860</v>
       </c>
       <c r="I41" t="n">
-        <v>2383</v>
+        <v>2535</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1506</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2983</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3091</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2848</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2803</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2450</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1357</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2923</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2821</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2974</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OTA - NANGANALLUR ROAD</t>
+          <t>TOLLGATE METRO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3145</v>
+        <v>2730</v>
       </c>
       <c r="C42" t="n">
-        <v>1095</v>
+        <v>1829</v>
       </c>
       <c r="D42" t="n">
-        <v>3091</v>
+        <v>2698</v>
       </c>
       <c r="E42" t="n">
-        <v>3162</v>
+        <v>2679</v>
       </c>
       <c r="F42" t="n">
-        <v>3204</v>
+        <v>2919</v>
       </c>
       <c r="G42" t="n">
-        <v>3270</v>
+        <v>2684</v>
       </c>
       <c r="H42" t="n">
-        <v>2999</v>
+        <v>2510</v>
       </c>
       <c r="I42" t="n">
-        <v>2119</v>
+        <v>2383</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2097</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2854</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2771</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2339</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2919</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2623</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2680</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2060</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2898</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2765</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2828</v>
       </c>
     </row>
   </sheetData>
@@ -2066,19 +3716,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31591.8</v>
+        <v>31316.46153846154</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1282.177912771858</v>
+        <v>1969.324783412858</v>
       </c>
       <c r="E2" t="n">
-        <v>24336</v>
+        <v>24397.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7703264771238106</v>
+        <v>0.7790535329170699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2106,19 +3756,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19584.4</v>
+        <v>19134.46153846154</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>683.5943972854074</v>
+        <v>743.5858631640575</v>
       </c>
       <c r="E3" t="n">
-        <v>17076</v>
+        <v>16896.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8719184657176119</v>
+        <v>0.8830454918230497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2146,19 +3796,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19346.8</v>
+        <v>18693.53846153846</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>322.2665046200113</v>
+        <v>1546.163726527941</v>
       </c>
       <c r="E4" t="n">
-        <v>8040</v>
+        <v>7987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4155726011536791</v>
+        <v>0.4272599335023208</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2182,27 +3832,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GUINDY</t>
+          <t>THIRUMANGALAM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17470.2</v>
+        <v>17151.23076923077</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>263.1733269159319</v>
+        <v>841.6801801403099</v>
       </c>
       <c r="E5" t="n">
-        <v>10916</v>
+        <v>11656.4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6248354340534167</v>
+        <v>0.6796246961420126</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Guindy</t>
+          <t>Thirumangalam</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2222,27 +3872,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THIRUMANGALAM</t>
+          <t>GUINDY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17411.6</v>
+        <v>16985.76923076923</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>371.5209280780828</v>
+        <v>987.1355153376992</v>
       </c>
       <c r="E6" t="n">
-        <v>11646</v>
+        <v>11069.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6688644352041169</v>
+        <v>0.651686706066164</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thirumangalam</t>
+          <t>Guindy</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2266,19 +3916,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13837.6</v>
+        <v>13786.15384615385</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>508.3687637925841</v>
+        <v>957.4617351930958</v>
       </c>
       <c r="E7" t="n">
-        <v>10813</v>
+        <v>10520.4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7814216338093311</v>
+        <v>0.7631134917977904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2306,19 +3956,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13793.6</v>
+        <v>13711.76923076923</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>770.4312428763517</v>
+        <v>632.6411771093935</v>
       </c>
       <c r="E8" t="n">
-        <v>12769</v>
+        <v>12924.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.925719174109732</v>
+        <v>0.9425625375169002</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2346,19 +3996,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13784</v>
+        <v>13544</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>731.76191483296</v>
+        <v>2196.949627703528</v>
       </c>
       <c r="E9" t="n">
-        <v>6502.5</v>
+        <v>6162.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4717426001160766</v>
+        <v>0.4550206733608978</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2386,19 +4036,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13223.6</v>
+        <v>12841.30769230769</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>198.8776005486791</v>
+        <v>619.9306929831464</v>
       </c>
       <c r="E10" t="n">
-        <v>8944.5</v>
+        <v>8954</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6764043074503161</v>
+        <v>0.6972810102014533</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2426,19 +4076,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11454.8</v>
+        <v>11290.53846153846</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>661.7535039574778</v>
+        <v>1212.100423190024</v>
       </c>
       <c r="E11" t="n">
-        <v>4912</v>
+        <v>4846.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.428815867583895</v>
+        <v>0.4292620778459841</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2462,27 +4112,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEYNAMPET</t>
+          <t>GOVERNMENT ESTATE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10882</v>
+        <v>10695.61538461538</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>164.9560547539859</v>
+        <v>658.5507495581412</v>
       </c>
       <c r="E12" t="n">
-        <v>4822</v>
+        <v>6985</v>
       </c>
       <c r="F12" t="n">
-        <v>0.443117074067267</v>
+        <v>0.65307135202779</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Teynampet</t>
+          <t>Government Estate</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2502,27 +4152,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOVERNMENT ESTATE</t>
+          <t>TEYNAMPET</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10870.4</v>
+        <v>10579.76923076923</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>265.6281235110469</v>
+        <v>892.0870803763266</v>
       </c>
       <c r="E13" t="n">
-        <v>7514.5</v>
+        <v>4740.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6912809096261407</v>
+        <v>0.448043799123145</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Government Estate</t>
+          <t>Teynampet</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2546,19 +4196,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9871.4</v>
+        <v>9565.615384615385</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>124.5604271026718</v>
+        <v>844.1753903920612</v>
       </c>
       <c r="E14" t="n">
-        <v>6660</v>
+        <v>6287.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6746763377028588</v>
+        <v>0.6573126502778381</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2586,19 +4236,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9760.6</v>
+        <v>9527.846153846154</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>432.8051524647089</v>
+        <v>493.942784499353</v>
       </c>
       <c r="E15" t="n">
-        <v>4147.5</v>
+        <v>4027.6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4249226481978567</v>
+        <v>0.422718832248793</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2626,19 +4276,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9633.6</v>
+        <v>8976.846153846154</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>338.5148445784911</v>
+        <v>1110.356687897621</v>
       </c>
       <c r="E16" t="n">
-        <v>3996</v>
+        <v>3697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4147982062780269</v>
+        <v>0.411837290807976</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2666,19 +4316,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8829.200000000001</v>
+        <v>8673.384615384615</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>179.1583098826286</v>
+        <v>412.1629003322066</v>
       </c>
       <c r="E17" t="n">
-        <v>6565.5</v>
+        <v>6456.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7436121052870022</v>
+        <v>0.7444152757330117</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2706,19 +4356,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8453.4</v>
+        <v>8261.76923076923</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>225.3226575380292</v>
+        <v>632.1040465311274</v>
       </c>
       <c r="E18" t="n">
-        <v>5240</v>
+        <v>5168.2</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6198689284784821</v>
+        <v>0.6255560831634126</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2746,19 +4396,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8330.200000000001</v>
+        <v>8075.846153846154</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>209.7503277709</v>
+        <v>700.4031988973505</v>
       </c>
       <c r="E19" t="n">
-        <v>3285.5</v>
+        <v>3477.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3944082975198674</v>
+        <v>0.4306421808622102</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2786,19 +4436,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7893.6</v>
+        <v>7793.307692307692</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>283.3766045389069</v>
+        <v>453.174430106735</v>
       </c>
       <c r="E20" t="n">
-        <v>6788</v>
+        <v>6643</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8599371642849903</v>
+        <v>0.8523980140751927</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2826,19 +4476,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7839.2</v>
+        <v>7665.307692307692</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>300.9629545309521</v>
+        <v>459.0452745672959</v>
       </c>
       <c r="E21" t="n">
-        <v>4267</v>
+        <v>4476.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5443157465047453</v>
+        <v>0.583955684452428</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2866,19 +4516,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7676</v>
+        <v>7415.923076923077</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>188.5417725598229</v>
+        <v>746.3114253378034</v>
       </c>
       <c r="E22" t="n">
-        <v>5402</v>
+        <v>5240.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7037519541427827</v>
+        <v>0.7066416339062516</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2906,19 +4556,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7653.2</v>
+        <v>7372.076923076923</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>222.3121679081017</v>
+        <v>886.9474300034606</v>
       </c>
       <c r="E23" t="n">
-        <v>4037</v>
+        <v>3913.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5274917681492709</v>
+        <v>0.5308137775598151</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2946,19 +4596,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7248.4</v>
+        <v>7153.538461538462</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>349.6252279227</v>
+        <v>425.9950342794728</v>
       </c>
       <c r="E24" t="n">
-        <v>4834</v>
+        <v>4840.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6669057999006678</v>
+        <v>0.6766441567379241</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2986,19 +4636,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7219.8</v>
+        <v>7121.769230769231</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>161.2318206806585</v>
+        <v>485.2338188691706</v>
       </c>
       <c r="E25" t="n">
-        <v>5281</v>
+        <v>5358.4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7314607052826948</v>
+        <v>0.7523973083611462</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3022,27 +4672,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANNADI</t>
+          <t>TONDIARPET METRO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7025.8</v>
+        <v>6936.384615384615</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>221.5303590932854</v>
+        <v>410.1937628449793</v>
       </c>
       <c r="E26" t="n">
-        <v>4586.5</v>
+        <v>4933.8</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6528082211278431</v>
+        <v>0.7112927372938685</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mannadi</t>
+          <t>Tondiarpet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3062,27 +4712,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TONDIARPET METRO</t>
+          <t>MANNADI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7020</v>
+        <v>6835.846153846154</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>173.9798838946618</v>
+        <v>501.3794049343349</v>
       </c>
       <c r="E27" t="n">
-        <v>4928.5</v>
+        <v>4509.6</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7020655270655271</v>
+        <v>0.6596988724596584</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tondiarpet</t>
+          <t>Mannadi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3106,19 +4756,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6555.6</v>
+        <v>6433.153846153846</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>320.8485624091216</v>
+        <v>377.373344349652</v>
       </c>
       <c r="E28" t="n">
-        <v>4759</v>
+        <v>4671.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7259442308865702</v>
+        <v>0.7261135224976385</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3146,19 +4796,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6248.2</v>
+        <v>6231.384615384615</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>111.5871856442307</v>
+        <v>317.8156012694412</v>
       </c>
       <c r="E29" t="n">
-        <v>5193.5</v>
+        <v>5353.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8311993854230019</v>
+        <v>0.859102804661268</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3182,27 +4832,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WIMCO NAGAR METRO</t>
+          <t>EGMORE</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5847</v>
+        <v>5761.307692307692</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>130.7191646240137</v>
+        <v>286.9153140491065</v>
       </c>
       <c r="E30" t="n">
-        <v>4019</v>
+        <v>5104.6</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6873610398494955</v>
+        <v>0.8860141260664647</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Wimco Nagar</t>
+          <t>Egmore</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3222,27 +4872,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EGMORE</t>
+          <t>WIMCO NAGAR METRO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5757.4</v>
+        <v>5760</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>192.8582380921282</v>
+        <v>349.0883364804195</v>
       </c>
       <c r="E31" t="n">
-        <v>5196.5</v>
+        <v>3961.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.902577552367388</v>
+        <v>0.6877777777777777</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Egmore</t>
+          <t>Wimco Nagar</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3266,19 +4916,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5446</v>
+        <v>5380.461538461538</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>82.71940522029882</v>
+        <v>348.6231526506847</v>
       </c>
       <c r="E32" t="n">
-        <v>4074.5</v>
+        <v>4071.2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7481637899375688</v>
+        <v>0.7566637120064049</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3306,19 +4956,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5327.6</v>
+        <v>5274.23076923077</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>197.4140319227588</v>
+        <v>167.5480795901853</v>
       </c>
       <c r="E33" t="n">
-        <v>4009</v>
+        <v>3992.4</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7524964336661911</v>
+        <v>0.7569634653248741</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3346,19 +4996,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5195.6</v>
+        <v>5045.23076923077</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>121.7345472739765</v>
+        <v>356.290413812046</v>
       </c>
       <c r="E34" t="n">
-        <v>3585</v>
+        <v>3623.6</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6900069289398721</v>
+        <v>0.7182228456424955</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3386,19 +5036,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4931.8</v>
+        <v>4912.076923076923</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>170.8294471102684</v>
+        <v>303.0345034091171</v>
       </c>
       <c r="E35" t="n">
-        <v>3678</v>
+        <v>3836.8</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7457723346445516</v>
+        <v>0.7810952597209391</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3426,19 +5076,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3741.8</v>
+        <v>3691.538461538461</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>160.6321885550963</v>
+        <v>248.4007566361985</v>
       </c>
       <c r="E36" t="n">
-        <v>2520.5</v>
+        <v>2546.6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6736062857448286</v>
+        <v>0.6898478849760367</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3466,19 +5116,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3285.6</v>
+        <v>3299.153846153846</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>264.3109910692327</v>
+        <v>343.9626545023568</v>
       </c>
       <c r="E37" t="n">
-        <v>1984.5</v>
+        <v>2130.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6039992695398101</v>
+        <v>0.6457413322763412</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3502,27 +5152,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NEHRU PARK</t>
+          <t>OTA - NANGANALLUR ROAD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3196.8</v>
+        <v>3118.307692307692</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>127.9363122807595</v>
+        <v>257.8359894116752</v>
       </c>
       <c r="E38" t="n">
-        <v>2477</v>
+        <v>1673</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7748373373373373</v>
+        <v>0.5365089545611524</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nehru Park</t>
+          <t>Nanganallur Road</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3542,27 +5192,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OTA - NANGANALLUR ROAD</t>
+          <t>NEHRU PARK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3145.2</v>
+        <v>3115.538461538461</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>104.435147340347</v>
+        <v>179.6940062924636</v>
       </c>
       <c r="E39" t="n">
-        <v>1607</v>
+        <v>2433.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.510937301284497</v>
+        <v>0.7809885931558935</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nanganallur Road</t>
+          <t>Nehru Park</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3586,19 +5236,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2962.8</v>
+        <v>2912.076923076923</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>67.39213603974881</v>
+        <v>127.0560647499506</v>
       </c>
       <c r="E40" t="n">
-        <v>1914.5</v>
+        <v>1828.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6461792898609423</v>
+        <v>0.6278680296906781</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3626,19 +5276,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2698</v>
+        <v>2729.769230769231</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>145.5523960640978</v>
+        <v>169.8092821599935</v>
       </c>
       <c r="E41" t="n">
-        <v>2106</v>
+        <v>2209.8</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7805782060785768</v>
+        <v>0.809518978780962</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3670,7 +5320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3680,6 +5330,17 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3718,6 +5379,61 @@
           <t>2026-08-22 Sat</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 Sun</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-24 Mon</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-25 Tue</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-26 Wed</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 Thu</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 Fri</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 Sat</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 Sun</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 Mon</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01 Tue</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02 Wed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3741,6 +5457,39 @@
       <c r="G2" t="n">
         <v>33</v>
       </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>58</v>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>117</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3764,6 +5513,39 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3787,6 +5569,39 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1071</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>865</v>
+      </c>
+      <c r="M4" t="n">
+        <v>790</v>
+      </c>
+      <c r="N4" t="n">
+        <v>901</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1252</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>869</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3810,6 +5625,39 @@
       <c r="G5" t="n">
         <v>1038</v>
       </c>
+      <c r="H5" t="n">
+        <v>860</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3805</v>
+      </c>
+      <c r="J5" t="n">
+        <v>860</v>
+      </c>
+      <c r="K5" t="n">
+        <v>778</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3494</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3148</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O5" t="n">
+        <v>788</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4032</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3090</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3833,6 +5681,39 @@
       <c r="G6" t="n">
         <v>3956</v>
       </c>
+      <c r="H6" t="n">
+        <v>3624</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3080</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8950</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6169</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6080</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3422</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7439</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3563</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6134</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3856,6 +5737,39 @@
       <c r="G7" t="n">
         <v>6458</v>
       </c>
+      <c r="H7" t="n">
+        <v>5807</v>
+      </c>
+      <c r="I7" t="n">
+        <v>18166</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6915</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8623</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17707</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15875</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9393</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5605</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15607</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7105</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14788</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3879,6 +5793,39 @@
       <c r="G8" t="n">
         <v>10931</v>
       </c>
+      <c r="H8" t="n">
+        <v>7355</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17050</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11700</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30491</v>
+      </c>
+      <c r="M8" t="n">
+        <v>28935</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18060</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6922</v>
+      </c>
+      <c r="P8" t="n">
+        <v>30698</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15020</v>
+      </c>
+      <c r="R8" t="n">
+        <v>31752</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3902,6 +5849,39 @@
       <c r="G9" t="n">
         <v>19639</v>
       </c>
+      <c r="H9" t="n">
+        <v>9214</v>
+      </c>
+      <c r="I9" t="n">
+        <v>46325</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31480</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21092</v>
+      </c>
+      <c r="L9" t="n">
+        <v>45002</v>
+      </c>
+      <c r="M9" t="n">
+        <v>43372</v>
+      </c>
+      <c r="N9" t="n">
+        <v>28978</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9007</v>
+      </c>
+      <c r="P9" t="n">
+        <v>47220</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>31966</v>
+      </c>
+      <c r="R9" t="n">
+        <v>47702</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3925,6 +5905,39 @@
       <c r="G10" t="n">
         <v>24292</v>
       </c>
+      <c r="H10" t="n">
+        <v>11188</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31637</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47842</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32443</v>
+      </c>
+      <c r="L10" t="n">
+        <v>29620</v>
+      </c>
+      <c r="M10" t="n">
+        <v>28647</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20346</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11484</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30826</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>48274</v>
+      </c>
+      <c r="R10" t="n">
+        <v>31820</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3948,6 +5961,39 @@
       <c r="G11" t="n">
         <v>19413</v>
       </c>
+      <c r="H11" t="n">
+        <v>12436</v>
+      </c>
+      <c r="I11" t="n">
+        <v>17315</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31841</v>
+      </c>
+      <c r="K11" t="n">
+        <v>22703</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16248</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15374</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14597</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12375</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16718</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>31389</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15896</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3971,6 +6017,39 @@
       <c r="G12" t="n">
         <v>15330</v>
       </c>
+      <c r="H12" t="n">
+        <v>12484</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15396</v>
+      </c>
+      <c r="J12" t="n">
+        <v>16612</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14487</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14740</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14876</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15171</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11531</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15343</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>15430</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14533</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3994,6 +6073,39 @@
       <c r="G13" t="n">
         <v>14812</v>
       </c>
+      <c r="H13" t="n">
+        <v>13635</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18795</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15641</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13744</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19862</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17665</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16320</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12409</v>
+      </c>
+      <c r="P13" t="n">
+        <v>18770</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>14195</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18263</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4017,6 +6129,39 @@
       <c r="G14" t="n">
         <v>17200</v>
       </c>
+      <c r="H14" t="n">
+        <v>13976</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19574</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18671</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15586</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18823</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17366</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17956</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12941</v>
+      </c>
+      <c r="P14" t="n">
+        <v>18769</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>17757</v>
+      </c>
+      <c r="R14" t="n">
+        <v>17914</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4040,6 +6185,39 @@
       <c r="G15" t="n">
         <v>21046</v>
       </c>
+      <c r="H15" t="n">
+        <v>14010</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15317</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17465</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15205</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14829</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16743</v>
+      </c>
+      <c r="O15" t="n">
+        <v>13727</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13767</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>17169</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14503</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4063,6 +6241,39 @@
       <c r="G16" t="n">
         <v>18938</v>
       </c>
+      <c r="H16" t="n">
+        <v>13923</v>
+      </c>
+      <c r="I16" t="n">
+        <v>17624</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16417</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13969</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17426</v>
+      </c>
+      <c r="M16" t="n">
+        <v>16917</v>
+      </c>
+      <c r="N16" t="n">
+        <v>19530</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12768</v>
+      </c>
+      <c r="P16" t="n">
+        <v>15991</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15168</v>
+      </c>
+      <c r="R16" t="n">
+        <v>16290</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4086,6 +6297,39 @@
       <c r="G17" t="n">
         <v>19047</v>
       </c>
+      <c r="H17" t="n">
+        <v>14389</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25118</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17224</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14939</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24894</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25356</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24377</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13427</v>
+      </c>
+      <c r="P17" t="n">
+        <v>24388</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16501</v>
+      </c>
+      <c r="R17" t="n">
+        <v>24260</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4109,6 +6353,39 @@
       <c r="G18" t="n">
         <v>22636</v>
       </c>
+      <c r="H18" t="n">
+        <v>14939</v>
+      </c>
+      <c r="I18" t="n">
+        <v>39522</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25944</v>
+      </c>
+      <c r="K18" t="n">
+        <v>18682</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39730</v>
+      </c>
+      <c r="M18" t="n">
+        <v>38932</v>
+      </c>
+      <c r="N18" t="n">
+        <v>29436</v>
+      </c>
+      <c r="O18" t="n">
+        <v>14837</v>
+      </c>
+      <c r="P18" t="n">
+        <v>38329</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25021</v>
+      </c>
+      <c r="R18" t="n">
+        <v>41385</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4132,6 +6409,39 @@
       <c r="G19" t="n">
         <v>26928</v>
       </c>
+      <c r="H19" t="n">
+        <v>16524</v>
+      </c>
+      <c r="I19" t="n">
+        <v>35492</v>
+      </c>
+      <c r="J19" t="n">
+        <v>39695</v>
+      </c>
+      <c r="K19" t="n">
+        <v>28963</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38232</v>
+      </c>
+      <c r="M19" t="n">
+        <v>36638</v>
+      </c>
+      <c r="N19" t="n">
+        <v>27262</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16920</v>
+      </c>
+      <c r="P19" t="n">
+        <v>36047</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>40686</v>
+      </c>
+      <c r="R19" t="n">
+        <v>38484</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4155,6 +6465,39 @@
       <c r="G20" t="n">
         <v>26456</v>
       </c>
+      <c r="H20" t="n">
+        <v>14553</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21663</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38781</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30923</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26067</v>
+      </c>
+      <c r="M20" t="n">
+        <v>24267</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20768</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15742</v>
+      </c>
+      <c r="P20" t="n">
+        <v>23071</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>38362</v>
+      </c>
+      <c r="R20" t="n">
+        <v>24355</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4178,6 +6521,39 @@
       <c r="G21" t="n">
         <v>19958</v>
       </c>
+      <c r="H21" t="n">
+        <v>14209</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16801</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24075</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21418</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14840</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15303</v>
+      </c>
+      <c r="N21" t="n">
+        <v>16146</v>
+      </c>
+      <c r="O21" t="n">
+        <v>13811</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14435</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23459</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14035</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4201,6 +6577,39 @@
       <c r="G22" t="n">
         <v>16293</v>
       </c>
+      <c r="H22" t="n">
+        <v>13371</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7452</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13886</v>
+      </c>
+      <c r="K22" t="n">
+        <v>13405</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7007</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8083</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10701</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12849</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7537</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13173</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6744</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4224,6 +6633,39 @@
       <c r="G23" t="n">
         <v>9673</v>
       </c>
+      <c r="H23" t="n">
+        <v>8079</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1619</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6259</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7661</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1655</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2328</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3663</v>
+      </c>
+      <c r="O23" t="n">
+        <v>8021</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1943</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6070</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1699</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4243,6 +6685,27 @@
       <c r="G24" t="n">
         <v>2326</v>
       </c>
+      <c r="H24" t="n">
+        <v>2492</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>1673</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1845</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>2126</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>1519</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4255,7 +6718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4366,372 +6829,955 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46257</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="n">
-        <v>20788</v>
+        <v>164932</v>
       </c>
       <c r="C2" t="n">
-        <v>5832</v>
+        <v>97374</v>
       </c>
       <c r="D2" t="n">
-        <v>555</v>
+        <v>1538</v>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>2819</v>
       </c>
       <c r="F2" t="n">
-        <v>7652</v>
+        <v>24679</v>
       </c>
       <c r="G2" t="n">
-        <v>830</v>
+        <v>4187</v>
       </c>
       <c r="H2" t="n">
-        <v>1315</v>
+        <v>6192</v>
       </c>
       <c r="I2" t="n">
-        <v>762</v>
+        <v>3253</v>
       </c>
       <c r="J2" t="n">
-        <v>14956</v>
+        <v>67558</v>
       </c>
       <c r="K2" t="n">
-        <v>99</v>
+        <v>400</v>
       </c>
       <c r="L2" t="n">
-        <v>1533</v>
+        <v>11365</v>
       </c>
       <c r="M2" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="N2" t="n">
-        <v>2306</v>
+        <v>18365</v>
       </c>
       <c r="O2" t="n">
-        <v>142</v>
+        <v>1955</v>
       </c>
       <c r="P2" t="n">
-        <v>646</v>
+        <v>6523</v>
       </c>
       <c r="Q2" t="n">
-        <v>632</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46256</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="n">
-        <v>316406</v>
+        <v>384527</v>
       </c>
       <c r="C3" t="n">
-        <v>124632</v>
+        <v>218840</v>
       </c>
       <c r="D3" t="n">
-        <v>5716</v>
+        <v>3802</v>
       </c>
       <c r="E3" t="n">
-        <v>8403</v>
+        <v>6868</v>
       </c>
       <c r="F3" t="n">
-        <v>86961</v>
+        <v>64793</v>
       </c>
       <c r="G3" t="n">
-        <v>10983</v>
+        <v>10131</v>
       </c>
       <c r="H3" t="n">
-        <v>17156</v>
+        <v>14687</v>
       </c>
       <c r="I3" t="n">
-        <v>8701</v>
+        <v>7276</v>
       </c>
       <c r="J3" t="n">
-        <v>191774</v>
+        <v>165687</v>
       </c>
       <c r="K3" t="n">
-        <v>1271</v>
+        <v>939</v>
       </c>
       <c r="L3" t="n">
-        <v>29072</v>
+        <v>27572</v>
       </c>
       <c r="M3" t="n">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="N3" t="n">
-        <v>40994</v>
+        <v>42652</v>
       </c>
       <c r="O3" t="n">
-        <v>2108</v>
+        <v>4877</v>
       </c>
       <c r="P3" t="n">
-        <v>10423</v>
+        <v>13971</v>
       </c>
       <c r="Q3" t="n">
-        <v>10752</v>
+        <v>10601</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46255</v>
+        <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>381292</v>
+        <v>382870</v>
       </c>
       <c r="C4" t="n">
-        <v>198771</v>
+        <v>217852</v>
       </c>
       <c r="D4" t="n">
-        <v>5481</v>
+        <v>3622</v>
       </c>
       <c r="E4" t="n">
-        <v>7805</v>
+        <v>6823</v>
       </c>
       <c r="F4" t="n">
-        <v>74795</v>
+        <v>64392</v>
       </c>
       <c r="G4" t="n">
-        <v>10831</v>
+        <v>10238</v>
       </c>
       <c r="H4" t="n">
-        <v>16459</v>
+        <v>14371</v>
       </c>
       <c r="I4" t="n">
-        <v>8819</v>
+        <v>7911</v>
       </c>
       <c r="J4" t="n">
-        <v>182521</v>
+        <v>165018</v>
       </c>
       <c r="K4" t="n">
-        <v>1202</v>
+        <v>1042</v>
       </c>
       <c r="L4" t="n">
-        <v>27567</v>
+        <v>26933</v>
       </c>
       <c r="M4" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="N4" t="n">
-        <v>43532</v>
+        <v>42556</v>
       </c>
       <c r="O4" t="n">
-        <v>3828</v>
+        <v>4773</v>
       </c>
       <c r="P4" t="n">
-        <v>14590</v>
+        <v>14442</v>
       </c>
       <c r="Q4" t="n">
-        <v>10971</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="n">
-        <v>387172</v>
+        <v>382217</v>
       </c>
       <c r="C5" t="n">
-        <v>217252</v>
+        <v>207015</v>
       </c>
       <c r="D5" t="n">
-        <v>5531</v>
+        <v>4046</v>
       </c>
       <c r="E5" t="n">
-        <v>6849</v>
+        <v>7353</v>
       </c>
       <c r="F5" t="n">
-        <v>71140</v>
+        <v>71778</v>
       </c>
       <c r="G5" t="n">
-        <v>9830</v>
+        <v>10316</v>
       </c>
       <c r="H5" t="n">
-        <v>14407</v>
+        <v>15562</v>
       </c>
       <c r="I5" t="n">
-        <v>8176</v>
+        <v>8181</v>
       </c>
       <c r="J5" t="n">
-        <v>169920</v>
+        <v>175202</v>
       </c>
       <c r="K5" t="n">
-        <v>1124</v>
+        <v>1048</v>
       </c>
       <c r="L5" t="n">
-        <v>23675</v>
+        <v>27176</v>
       </c>
       <c r="M5" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="N5" t="n">
-        <v>39767</v>
+        <v>43235</v>
       </c>
       <c r="O5" t="n">
-        <v>4073</v>
+        <v>4166</v>
       </c>
       <c r="P5" t="n">
-        <v>14837</v>
+        <v>14891</v>
       </c>
       <c r="Q5" t="n">
-        <v>10147</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46253</v>
+        <v>46264</v>
       </c>
       <c r="B6" t="n">
-        <v>391553</v>
+        <v>210739</v>
       </c>
       <c r="C6" t="n">
-        <v>219797</v>
+        <v>58965</v>
       </c>
       <c r="D6" t="n">
-        <v>4933</v>
+        <v>4228</v>
       </c>
       <c r="E6" t="n">
-        <v>7035</v>
+        <v>6769</v>
       </c>
       <c r="F6" t="n">
-        <v>71160</v>
+        <v>72960</v>
       </c>
       <c r="G6" t="n">
-        <v>9746</v>
+        <v>8669</v>
       </c>
       <c r="H6" t="n">
-        <v>14375</v>
+        <v>13884</v>
       </c>
       <c r="I6" t="n">
-        <v>8379</v>
+        <v>6646</v>
       </c>
       <c r="J6" t="n">
-        <v>171756</v>
+        <v>151774</v>
       </c>
       <c r="K6" t="n">
-        <v>1072</v>
+        <v>1184</v>
       </c>
       <c r="L6" t="n">
-        <v>26087</v>
+        <v>21353</v>
       </c>
       <c r="M6" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="N6" t="n">
-        <v>41969</v>
+        <v>28960</v>
       </c>
       <c r="O6" t="n">
-        <v>4222</v>
+        <v>1197</v>
       </c>
       <c r="P6" t="n">
-        <v>14695</v>
+        <v>6316</v>
       </c>
       <c r="Q6" t="n">
-        <v>9937</v>
+        <v>8461</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46252</v>
+        <v>46263</v>
       </c>
       <c r="B7" t="n">
-        <v>390922</v>
+        <v>319952</v>
       </c>
       <c r="C7" t="n">
-        <v>219433</v>
+        <v>136163</v>
       </c>
       <c r="D7" t="n">
-        <v>4811</v>
+        <v>5035</v>
       </c>
       <c r="E7" t="n">
-        <v>6728</v>
+        <v>8628</v>
       </c>
       <c r="F7" t="n">
-        <v>70189</v>
+        <v>78142</v>
       </c>
       <c r="G7" t="n">
-        <v>9647</v>
+        <v>11141</v>
       </c>
       <c r="H7" t="n">
-        <v>14329</v>
+        <v>17333</v>
       </c>
       <c r="I7" t="n">
-        <v>9093</v>
+        <v>7832</v>
       </c>
       <c r="J7" t="n">
-        <v>171489</v>
+        <v>183789</v>
       </c>
       <c r="K7" t="n">
-        <v>1071</v>
+        <v>1400</v>
       </c>
       <c r="L7" t="n">
-        <v>26120</v>
+        <v>28659</v>
       </c>
       <c r="M7" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="N7" t="n">
-        <v>42297</v>
+        <v>41576</v>
       </c>
       <c r="O7" t="n">
-        <v>4511</v>
+        <v>2564</v>
       </c>
       <c r="P7" t="n">
-        <v>14986</v>
+        <v>11347</v>
       </c>
       <c r="Q7" t="n">
-        <v>9884</v>
+        <v>11538</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B8" t="n">
+        <v>374907</v>
+      </c>
+      <c r="C8" t="n">
+        <v>201431</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4411</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7169</v>
+      </c>
+      <c r="F8" t="n">
+        <v>70067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10461</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15504</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8093</v>
+      </c>
+      <c r="J8" t="n">
+        <v>173476</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26406</v>
+      </c>
+      <c r="M8" t="n">
+        <v>180</v>
+      </c>
+      <c r="N8" t="n">
+        <v>42950</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3869</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15301</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10952</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B9" t="n">
+        <v>390924</v>
+      </c>
+      <c r="C9" t="n">
+        <v>205884</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4691</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8066</v>
+      </c>
+      <c r="F9" t="n">
+        <v>85586</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10684</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15082</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8378</v>
+      </c>
+      <c r="J9" t="n">
+        <v>185040</v>
+      </c>
+      <c r="K9" t="n">
+        <v>645</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20970</v>
+      </c>
+      <c r="M9" t="n">
+        <v>167</v>
+      </c>
+      <c r="N9" t="n">
+        <v>38176</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4075</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16394</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10302</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B10" t="n">
+        <v>313528</v>
+      </c>
+      <c r="C10" t="n">
+        <v>139772</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4438</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6710</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79640</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9618</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14275</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7416</v>
+      </c>
+      <c r="J10" t="n">
+        <v>173756</v>
+      </c>
+      <c r="K10" t="n">
+        <v>499</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25487</v>
+      </c>
+      <c r="M10" t="n">
+        <v>145</v>
+      </c>
+      <c r="N10" t="n">
+        <v>38973</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2866</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12842</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9820</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B11" t="n">
+        <v>393530</v>
+      </c>
+      <c r="C11" t="n">
+        <v>215330</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3860</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6849</v>
+      </c>
+      <c r="F11" t="n">
+        <v>75189</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9886</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15146</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8025</v>
+      </c>
+      <c r="J11" t="n">
+        <v>178200</v>
+      </c>
+      <c r="K11" t="n">
+        <v>739</v>
+      </c>
+      <c r="L11" t="n">
+        <v>26854</v>
+      </c>
+      <c r="M11" t="n">
+        <v>141</v>
+      </c>
+      <c r="N11" t="n">
+        <v>44545</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4247</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16811</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10453</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B12" t="n">
+        <v>391543</v>
+      </c>
+      <c r="C12" t="n">
+        <v>209551</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5046</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7347</v>
+      </c>
+      <c r="F12" t="n">
+        <v>78886</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10048</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15478</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8347</v>
+      </c>
+      <c r="J12" t="n">
+        <v>181992</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1093</v>
+      </c>
+      <c r="L12" t="n">
+        <v>26578</v>
+      </c>
+      <c r="M12" t="n">
+        <v>131</v>
+      </c>
+      <c r="N12" t="n">
+        <v>43006</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4003</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15204</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9831</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B13" t="n">
+        <v>217114</v>
+      </c>
+      <c r="C13" t="n">
+        <v>58822</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5235</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7342</v>
+      </c>
+      <c r="F13" t="n">
+        <v>75913</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8686</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13977</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7252</v>
+      </c>
+      <c r="J13" t="n">
+        <v>158292</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1028</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22342</v>
+      </c>
+      <c r="M13" t="n">
+        <v>178</v>
+      </c>
+      <c r="N13" t="n">
+        <v>30090</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1086</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6542</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8711</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B14" t="n">
+        <v>316406</v>
+      </c>
+      <c r="C14" t="n">
+        <v>124632</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5716</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8403</v>
+      </c>
+      <c r="F14" t="n">
+        <v>86961</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10983</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17156</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8701</v>
+      </c>
+      <c r="J14" t="n">
+        <v>191774</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1271</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29072</v>
+      </c>
+      <c r="M14" t="n">
+        <v>228</v>
+      </c>
+      <c r="N14" t="n">
+        <v>40994</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2108</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10423</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10752</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B15" t="n">
+        <v>381292</v>
+      </c>
+      <c r="C15" t="n">
+        <v>198771</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5481</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7805</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74795</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10831</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16459</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8819</v>
+      </c>
+      <c r="J15" t="n">
+        <v>182521</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L15" t="n">
+        <v>27567</v>
+      </c>
+      <c r="M15" t="n">
+        <v>173</v>
+      </c>
+      <c r="N15" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3828</v>
+      </c>
+      <c r="P15" t="n">
+        <v>14590</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>10971</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B16" t="n">
+        <v>387172</v>
+      </c>
+      <c r="C16" t="n">
+        <v>217252</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5531</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6849</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71140</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9830</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14407</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8176</v>
+      </c>
+      <c r="J16" t="n">
+        <v>169920</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23675</v>
+      </c>
+      <c r="M16" t="n">
+        <v>131</v>
+      </c>
+      <c r="N16" t="n">
+        <v>39767</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4073</v>
+      </c>
+      <c r="P16" t="n">
+        <v>14837</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B17" t="n">
+        <v>391553</v>
+      </c>
+      <c r="C17" t="n">
+        <v>219797</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4933</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7035</v>
+      </c>
+      <c r="F17" t="n">
+        <v>71160</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9746</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14375</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8379</v>
+      </c>
+      <c r="J17" t="n">
+        <v>171756</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L17" t="n">
+        <v>26087</v>
+      </c>
+      <c r="M17" t="n">
+        <v>115</v>
+      </c>
+      <c r="N17" t="n">
+        <v>41969</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4222</v>
+      </c>
+      <c r="P17" t="n">
+        <v>14695</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9937</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B18" t="n">
+        <v>390922</v>
+      </c>
+      <c r="C18" t="n">
+        <v>219433</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6728</v>
+      </c>
+      <c r="F18" t="n">
+        <v>70189</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9647</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14329</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9093</v>
+      </c>
+      <c r="J18" t="n">
+        <v>171489</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26120</v>
+      </c>
+      <c r="M18" t="n">
+        <v>120</v>
+      </c>
+      <c r="N18" t="n">
+        <v>42297</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4511</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14986</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9884</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>46251</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B19" t="n">
         <v>393467</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C19" t="n">
         <v>211337</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D19" t="n">
         <v>5023</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E19" t="n">
         <v>7288</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F19" t="n">
         <v>79173</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G19" t="n">
         <v>10128</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H19" t="n">
         <v>15340</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I19" t="n">
         <v>9645</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J19" t="n">
         <v>182130</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K19" t="n">
         <v>1053</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L19" t="n">
         <v>25444</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M19" t="n">
         <v>168</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N19" t="n">
         <v>41658</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O19" t="n">
         <v>3998</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P19" t="n">
         <v>14993</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q19" t="n">
         <v>9877</v>
       </c>
     </row>

--- a/Mapathon/outputs/tables/cmrl_data.xlsx
+++ b/Mapathon/outputs/tables/cmrl_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>164932</v>
+        <v>42428</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
@@ -493,20 +493,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>379454</v>
+        <v>297523</v>
       </c>
       <c r="E3" t="n">
         <v>41</v>
@@ -514,11 +514,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>377033</v>
+        <v>275508</v>
       </c>
       <c r="E4" t="n">
         <v>41</v>
@@ -535,11 +535,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>375609</v>
+        <v>387805</v>
       </c>
       <c r="E5" t="n">
         <v>41</v>
@@ -556,20 +556,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>206719</v>
+        <v>379454</v>
       </c>
       <c r="E6" t="n">
         <v>41</v>
@@ -577,20 +577,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>315226</v>
+        <v>377033</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -598,11 +598,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>368873</v>
+        <v>375609</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
@@ -619,20 +619,20 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>372194</v>
+        <v>206719</v>
       </c>
       <c r="E9" t="n">
         <v>41</v>
@@ -640,20 +640,20 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>295293</v>
+        <v>315226</v>
       </c>
       <c r="E10" t="n">
         <v>41</v>
@@ -661,11 +661,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>379448</v>
+        <v>368873</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
@@ -682,11 +682,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>378136</v>
+        <v>372194</v>
       </c>
       <c r="E12" t="n">
         <v>41</v>
@@ -703,20 +703,20 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>217114</v>
+        <v>295293</v>
       </c>
       <c r="E13" t="n">
         <v>41</v>
@@ -724,20 +724,20 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>306203</v>
+        <v>379448</v>
       </c>
       <c r="E14" t="n">
         <v>41</v>
@@ -745,11 +745,11 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>372199</v>
+        <v>378136</v>
       </c>
       <c r="E15" t="n">
         <v>41</v>
@@ -766,20 +766,20 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>377617</v>
+        <v>217114</v>
       </c>
       <c r="E16" t="n">
         <v>41</v>
@@ -787,20 +787,20 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>381888</v>
+        <v>306203</v>
       </c>
       <c r="E17" t="n">
         <v>41</v>
@@ -808,11 +808,11 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>379824</v>
+        <v>372199</v>
       </c>
       <c r="E18" t="n">
         <v>41</v>
@@ -829,11 +829,11 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>376881</v>
+        <v>377617</v>
       </c>
       <c r="E19" t="n">
         <v>41</v>
@@ -850,22 +850,85 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>381888</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>379824</v>
+      </c>
+      <c r="E21" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>376881</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>46250</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>weekend</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D23" t="n">
         <v>192613</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E23" t="n">
         <v>41</v>
       </c>
     </row>
@@ -880,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -903,6 +966,9 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1006,6 +1072,21 @@
           <t>2026-09-02 Wed</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03 Thu</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 Fri</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 Sat</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1014,7 +1095,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31316</v>
+        <v>30998</v>
       </c>
       <c r="C2" t="n">
         <v>20610</v>
@@ -1070,133 +1151,160 @@
       <c r="T2" t="n">
         <v>31706</v>
       </c>
+      <c r="U2" t="n">
+        <v>32741</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25112</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27379</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>THOUSAND LIGHT</t>
+          <t>CHENNAI AIRPORT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18694</v>
+        <v>19028</v>
       </c>
       <c r="C3" t="n">
-        <v>5047</v>
+        <v>15071</v>
       </c>
       <c r="D3" t="n">
-        <v>19138</v>
+        <v>19893</v>
       </c>
       <c r="E3" t="n">
-        <v>19507</v>
+        <v>19042</v>
       </c>
       <c r="F3" t="n">
-        <v>19692</v>
+        <v>19230</v>
       </c>
       <c r="G3" t="n">
-        <v>19501</v>
+        <v>19110</v>
       </c>
       <c r="H3" t="n">
-        <v>18896</v>
+        <v>20647</v>
       </c>
       <c r="I3" t="n">
-        <v>11033</v>
+        <v>19081</v>
       </c>
       <c r="J3" t="n">
-        <v>5005</v>
+        <v>15971</v>
       </c>
       <c r="K3" t="n">
-        <v>18987</v>
+        <v>19113</v>
       </c>
       <c r="L3" t="n">
-        <v>19510</v>
+        <v>18883</v>
       </c>
       <c r="M3" t="n">
-        <v>13740</v>
+        <v>17288</v>
       </c>
       <c r="N3" t="n">
-        <v>18617</v>
+        <v>19033</v>
       </c>
       <c r="O3" t="n">
-        <v>18322</v>
+        <v>19531</v>
       </c>
       <c r="P3" t="n">
-        <v>13264</v>
+        <v>18898</v>
       </c>
       <c r="Q3" t="n">
-        <v>5586</v>
+        <v>15462</v>
       </c>
       <c r="R3" t="n">
-        <v>18616</v>
+        <v>19180</v>
       </c>
       <c r="S3" t="n">
-        <v>19033</v>
+        <v>18900</v>
       </c>
       <c r="T3" t="n">
-        <v>19457</v>
+        <v>18898</v>
+      </c>
+      <c r="U3" t="n">
+        <v>19747</v>
+      </c>
+      <c r="V3" t="n">
+        <v>16921</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHENNAI AIRPORT</t>
+          <t>VADAPALANI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19134</v>
+        <v>13619</v>
       </c>
       <c r="C4" t="n">
-        <v>15071</v>
+        <v>10793</v>
       </c>
       <c r="D4" t="n">
-        <v>19893</v>
+        <v>13040</v>
       </c>
       <c r="E4" t="n">
-        <v>19042</v>
+        <v>14945</v>
       </c>
       <c r="F4" t="n">
-        <v>19230</v>
+        <v>13565</v>
       </c>
       <c r="G4" t="n">
-        <v>19110</v>
+        <v>13254</v>
       </c>
       <c r="H4" t="n">
-        <v>20647</v>
+        <v>14164</v>
       </c>
       <c r="I4" t="n">
-        <v>19081</v>
+        <v>14745</v>
       </c>
       <c r="J4" t="n">
-        <v>15971</v>
+        <v>12846</v>
       </c>
       <c r="K4" t="n">
-        <v>19113</v>
+        <v>12906</v>
       </c>
       <c r="L4" t="n">
-        <v>18883</v>
+        <v>14423</v>
       </c>
       <c r="M4" t="n">
-        <v>17288</v>
+        <v>13576</v>
       </c>
       <c r="N4" t="n">
-        <v>19033</v>
+        <v>13305</v>
       </c>
       <c r="O4" t="n">
-        <v>19531</v>
+        <v>13879</v>
       </c>
       <c r="P4" t="n">
-        <v>18898</v>
+        <v>14218</v>
       </c>
       <c r="Q4" t="n">
-        <v>15462</v>
+        <v>12019</v>
       </c>
       <c r="R4" t="n">
-        <v>19180</v>
+        <v>13265</v>
       </c>
       <c r="S4" t="n">
-        <v>18900</v>
+        <v>14557</v>
       </c>
       <c r="T4" t="n">
-        <v>18898</v>
+        <v>13374</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14402</v>
+      </c>
+      <c r="V4" t="n">
+        <v>11631</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14398</v>
       </c>
     </row>
     <row r="5">
@@ -1206,7 +1314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17151</v>
+        <v>16944</v>
       </c>
       <c r="C5" t="n">
         <v>9140</v>
@@ -1262,1989 +1370,2277 @@
       <c r="T5" t="n">
         <v>17648</v>
       </c>
+      <c r="U5" t="n">
+        <v>17845</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13356</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13988</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GUINDY</t>
+          <t>THOUSAND LIGHT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16986</v>
+        <v>18426</v>
       </c>
       <c r="C6" t="n">
-        <v>8360</v>
+        <v>5047</v>
       </c>
       <c r="D6" t="n">
-        <v>17372</v>
+        <v>19138</v>
       </c>
       <c r="E6" t="n">
-        <v>17056</v>
+        <v>19507</v>
       </c>
       <c r="F6" t="n">
-        <v>17628</v>
+        <v>19692</v>
       </c>
       <c r="G6" t="n">
-        <v>17711</v>
+        <v>19501</v>
       </c>
       <c r="H6" t="n">
-        <v>17584</v>
+        <v>18896</v>
       </c>
       <c r="I6" t="n">
-        <v>13472</v>
+        <v>11033</v>
       </c>
       <c r="J6" t="n">
-        <v>9649</v>
+        <v>5005</v>
       </c>
       <c r="K6" t="n">
-        <v>17223</v>
+        <v>18987</v>
       </c>
       <c r="L6" t="n">
-        <v>17309</v>
+        <v>19510</v>
       </c>
       <c r="M6" t="n">
-        <v>13844</v>
+        <v>13740</v>
       </c>
       <c r="N6" t="n">
-        <v>16913</v>
+        <v>18617</v>
       </c>
       <c r="O6" t="n">
-        <v>17140</v>
+        <v>18322</v>
       </c>
       <c r="P6" t="n">
-        <v>14631</v>
+        <v>13264</v>
       </c>
       <c r="Q6" t="n">
-        <v>9235</v>
+        <v>5586</v>
       </c>
       <c r="R6" t="n">
-        <v>17025</v>
+        <v>18616</v>
       </c>
       <c r="S6" t="n">
-        <v>16705</v>
+        <v>19033</v>
       </c>
       <c r="T6" t="n">
-        <v>17305</v>
+        <v>19457</v>
+      </c>
+      <c r="U6" t="n">
+        <v>20161</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13213</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12821</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KOYAMBEDU</t>
+          <t>GUINDY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13786</v>
+        <v>16802</v>
       </c>
       <c r="C7" t="n">
-        <v>9042</v>
+        <v>8360</v>
       </c>
       <c r="D7" t="n">
-        <v>14677</v>
+        <v>17372</v>
       </c>
       <c r="E7" t="n">
-        <v>13717</v>
+        <v>17056</v>
       </c>
       <c r="F7" t="n">
-        <v>13835</v>
+        <v>17628</v>
       </c>
       <c r="G7" t="n">
-        <v>13309</v>
+        <v>17711</v>
       </c>
       <c r="H7" t="n">
-        <v>13650</v>
+        <v>17584</v>
       </c>
       <c r="I7" t="n">
-        <v>12584</v>
+        <v>13472</v>
       </c>
       <c r="J7" t="n">
-        <v>9931</v>
+        <v>9649</v>
       </c>
       <c r="K7" t="n">
-        <v>14743</v>
+        <v>17223</v>
       </c>
       <c r="L7" t="n">
-        <v>14252</v>
+        <v>17309</v>
       </c>
       <c r="M7" t="n">
-        <v>10957</v>
+        <v>13844</v>
       </c>
       <c r="N7" t="n">
-        <v>13693</v>
+        <v>16913</v>
       </c>
       <c r="O7" t="n">
-        <v>13638</v>
+        <v>17140</v>
       </c>
       <c r="P7" t="n">
-        <v>11896</v>
+        <v>14631</v>
       </c>
       <c r="Q7" t="n">
-        <v>9149</v>
+        <v>9235</v>
       </c>
       <c r="R7" t="n">
-        <v>14557</v>
+        <v>17025</v>
       </c>
       <c r="S7" t="n">
-        <v>14108</v>
+        <v>16705</v>
       </c>
       <c r="T7" t="n">
-        <v>14084</v>
+        <v>17305</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17745</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13467</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HIGH COURT</t>
+          <t>KOYAMBEDU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13544</v>
+        <v>13529</v>
       </c>
       <c r="C8" t="n">
-        <v>3599</v>
+        <v>9042</v>
       </c>
       <c r="D8" t="n">
-        <v>13539</v>
+        <v>14677</v>
       </c>
       <c r="E8" t="n">
-        <v>14815</v>
+        <v>13717</v>
       </c>
       <c r="F8" t="n">
-        <v>14124</v>
+        <v>13835</v>
       </c>
       <c r="G8" t="n">
-        <v>13588</v>
+        <v>13309</v>
       </c>
       <c r="H8" t="n">
-        <v>12854</v>
+        <v>13650</v>
       </c>
       <c r="I8" t="n">
-        <v>9406</v>
+        <v>12584</v>
       </c>
       <c r="J8" t="n">
-        <v>4305</v>
+        <v>9931</v>
       </c>
       <c r="K8" t="n">
-        <v>13885</v>
+        <v>14743</v>
       </c>
       <c r="L8" t="n">
-        <v>14290</v>
+        <v>14252</v>
       </c>
       <c r="M8" t="n">
-        <v>7338</v>
+        <v>10957</v>
       </c>
       <c r="N8" t="n">
-        <v>17218</v>
+        <v>13693</v>
       </c>
       <c r="O8" t="n">
-        <v>12784</v>
+        <v>13638</v>
       </c>
       <c r="P8" t="n">
-        <v>9909</v>
+        <v>11896</v>
       </c>
       <c r="Q8" t="n">
-        <v>3595</v>
+        <v>9149</v>
       </c>
       <c r="R8" t="n">
-        <v>13042</v>
+        <v>14557</v>
       </c>
       <c r="S8" t="n">
-        <v>14945</v>
+        <v>14108</v>
       </c>
       <c r="T8" t="n">
-        <v>13650</v>
+        <v>14084</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14227</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9492</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VADAPALANI</t>
+          <t>ALANDUR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13712</v>
+        <v>12668</v>
       </c>
       <c r="C9" t="n">
-        <v>10793</v>
+        <v>6875</v>
       </c>
       <c r="D9" t="n">
-        <v>13040</v>
+        <v>12980</v>
       </c>
       <c r="E9" t="n">
-        <v>14945</v>
+        <v>13355</v>
       </c>
       <c r="F9" t="n">
-        <v>13565</v>
+        <v>13488</v>
       </c>
       <c r="G9" t="n">
-        <v>13254</v>
+        <v>13140</v>
       </c>
       <c r="H9" t="n">
-        <v>14164</v>
+        <v>13155</v>
       </c>
       <c r="I9" t="n">
-        <v>14745</v>
+        <v>11014</v>
       </c>
       <c r="J9" t="n">
-        <v>12846</v>
+        <v>7839</v>
       </c>
       <c r="K9" t="n">
-        <v>12906</v>
+        <v>12821</v>
       </c>
       <c r="L9" t="n">
-        <v>14423</v>
+        <v>13074</v>
       </c>
       <c r="M9" t="n">
-        <v>13576</v>
+        <v>11035</v>
       </c>
       <c r="N9" t="n">
-        <v>13305</v>
+        <v>12312</v>
       </c>
       <c r="O9" t="n">
-        <v>13879</v>
+        <v>12687</v>
       </c>
       <c r="P9" t="n">
-        <v>14218</v>
+        <v>11443</v>
       </c>
       <c r="Q9" t="n">
-        <v>12019</v>
+        <v>7599</v>
       </c>
       <c r="R9" t="n">
-        <v>13265</v>
+        <v>12769</v>
       </c>
       <c r="S9" t="n">
-        <v>14557</v>
+        <v>13050</v>
       </c>
       <c r="T9" t="n">
-        <v>13374</v>
+        <v>13071</v>
+      </c>
+      <c r="U9" t="n">
+        <v>13301</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9786</v>
+      </c>
+      <c r="W9" t="n">
+        <v>10188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALANDUR</t>
+          <t>HIGH COURT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12841</v>
+        <v>13151</v>
       </c>
       <c r="C10" t="n">
-        <v>6875</v>
+        <v>3599</v>
       </c>
       <c r="D10" t="n">
-        <v>12980</v>
+        <v>13539</v>
       </c>
       <c r="E10" t="n">
-        <v>13355</v>
+        <v>14815</v>
       </c>
       <c r="F10" t="n">
-        <v>13488</v>
+        <v>14124</v>
       </c>
       <c r="G10" t="n">
-        <v>13140</v>
+        <v>13588</v>
       </c>
       <c r="H10" t="n">
-        <v>13155</v>
+        <v>12854</v>
       </c>
       <c r="I10" t="n">
-        <v>11014</v>
+        <v>9406</v>
       </c>
       <c r="J10" t="n">
-        <v>7839</v>
+        <v>4305</v>
       </c>
       <c r="K10" t="n">
-        <v>12821</v>
+        <v>13885</v>
       </c>
       <c r="L10" t="n">
-        <v>13074</v>
+        <v>14290</v>
       </c>
       <c r="M10" t="n">
-        <v>11035</v>
+        <v>7338</v>
       </c>
       <c r="N10" t="n">
-        <v>12312</v>
+        <v>17218</v>
       </c>
       <c r="O10" t="n">
-        <v>12687</v>
+        <v>12784</v>
       </c>
       <c r="P10" t="n">
-        <v>11443</v>
+        <v>9909</v>
       </c>
       <c r="Q10" t="n">
-        <v>7599</v>
+        <v>3595</v>
       </c>
       <c r="R10" t="n">
-        <v>12769</v>
+        <v>13042</v>
       </c>
       <c r="S10" t="n">
-        <v>13050</v>
+        <v>14945</v>
       </c>
       <c r="T10" t="n">
-        <v>13071</v>
+        <v>13650</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13866</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7325</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>GOVERNMENT ESTATE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11291</v>
+        <v>10538</v>
       </c>
       <c r="C11" t="n">
-        <v>3680</v>
+        <v>5081</v>
       </c>
       <c r="D11" t="n">
-        <v>11469</v>
+        <v>10634</v>
       </c>
       <c r="E11" t="n">
-        <v>11774</v>
+        <v>11172</v>
       </c>
       <c r="F11" t="n">
-        <v>11846</v>
+        <v>11076</v>
       </c>
       <c r="G11" t="n">
-        <v>11878</v>
+        <v>10903</v>
       </c>
       <c r="H11" t="n">
-        <v>10307</v>
+        <v>10567</v>
       </c>
       <c r="I11" t="n">
-        <v>6144</v>
+        <v>9948</v>
       </c>
       <c r="J11" t="n">
-        <v>3657</v>
+        <v>5610</v>
       </c>
       <c r="K11" t="n">
-        <v>11713</v>
+        <v>10635</v>
       </c>
       <c r="L11" t="n">
-        <v>11971</v>
+        <v>10855</v>
       </c>
       <c r="M11" t="n">
-        <v>7550</v>
+        <v>8733</v>
       </c>
       <c r="N11" t="n">
-        <v>11624</v>
+        <v>10912</v>
       </c>
       <c r="O11" t="n">
-        <v>11418</v>
+        <v>11587</v>
       </c>
       <c r="P11" t="n">
-        <v>7132</v>
+        <v>9284</v>
       </c>
       <c r="Q11" t="n">
-        <v>3620</v>
+        <v>5002</v>
       </c>
       <c r="R11" t="n">
-        <v>11272</v>
+        <v>10684</v>
       </c>
       <c r="S11" t="n">
-        <v>11838</v>
+        <v>10499</v>
       </c>
       <c r="T11" t="n">
-        <v>12117</v>
+        <v>10786</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10793</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8241</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEYNAMPET</t>
+          <t>LIC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10580</v>
+        <v>11068</v>
       </c>
       <c r="C12" t="n">
-        <v>2852</v>
+        <v>3680</v>
       </c>
       <c r="D12" t="n">
-        <v>10642</v>
+        <v>11469</v>
       </c>
       <c r="E12" t="n">
-        <v>10992</v>
+        <v>11774</v>
       </c>
       <c r="F12" t="n">
-        <v>11036</v>
+        <v>11846</v>
       </c>
       <c r="G12" t="n">
-        <v>10957</v>
+        <v>11878</v>
       </c>
       <c r="H12" t="n">
-        <v>10783</v>
+        <v>10307</v>
       </c>
       <c r="I12" t="n">
-        <v>6792</v>
+        <v>6144</v>
       </c>
       <c r="J12" t="n">
-        <v>2889</v>
+        <v>3657</v>
       </c>
       <c r="K12" t="n">
-        <v>10901</v>
+        <v>11713</v>
       </c>
       <c r="L12" t="n">
-        <v>10854</v>
+        <v>11971</v>
       </c>
       <c r="M12" t="n">
-        <v>7659</v>
+        <v>7550</v>
       </c>
       <c r="N12" t="n">
-        <v>10754</v>
+        <v>11624</v>
       </c>
       <c r="O12" t="n">
-        <v>10759</v>
+        <v>11418</v>
       </c>
       <c r="P12" t="n">
-        <v>8192</v>
+        <v>7132</v>
       </c>
       <c r="Q12" t="n">
-        <v>2976</v>
+        <v>3620</v>
       </c>
       <c r="R12" t="n">
-        <v>10442</v>
+        <v>11272</v>
       </c>
       <c r="S12" t="n">
-        <v>10794</v>
+        <v>11838</v>
       </c>
       <c r="T12" t="n">
-        <v>10964</v>
+        <v>12117</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12285</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6960</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOVERNMENT ESTATE</t>
+          <t>ASHOK NAGAR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10696</v>
+        <v>9430</v>
       </c>
       <c r="C13" t="n">
-        <v>5081</v>
+        <v>4372</v>
       </c>
       <c r="D13" t="n">
-        <v>10634</v>
+        <v>9905</v>
       </c>
       <c r="E13" t="n">
-        <v>11172</v>
+        <v>9740</v>
       </c>
       <c r="F13" t="n">
-        <v>11076</v>
+        <v>10037</v>
       </c>
       <c r="G13" t="n">
-        <v>10903</v>
+        <v>9754</v>
       </c>
       <c r="H13" t="n">
-        <v>10567</v>
+        <v>9921</v>
       </c>
       <c r="I13" t="n">
-        <v>9948</v>
+        <v>8948</v>
       </c>
       <c r="J13" t="n">
-        <v>5610</v>
+        <v>5124</v>
       </c>
       <c r="K13" t="n">
-        <v>10635</v>
+        <v>10057</v>
       </c>
       <c r="L13" t="n">
-        <v>10855</v>
+        <v>10340</v>
       </c>
       <c r="M13" t="n">
-        <v>8733</v>
+        <v>7094</v>
       </c>
       <c r="N13" t="n">
-        <v>10912</v>
+        <v>8605</v>
       </c>
       <c r="O13" t="n">
-        <v>11587</v>
+        <v>9599</v>
       </c>
       <c r="P13" t="n">
-        <v>9284</v>
+        <v>7983</v>
       </c>
       <c r="Q13" t="n">
-        <v>5002</v>
+        <v>5011</v>
       </c>
       <c r="R13" t="n">
-        <v>10684</v>
+        <v>9643</v>
       </c>
       <c r="S13" t="n">
-        <v>10499</v>
+        <v>9788</v>
       </c>
       <c r="T13" t="n">
-        <v>10786</v>
+        <v>9870</v>
+      </c>
+      <c r="U13" t="n">
+        <v>10524</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6575</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7598</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EKKATTUTHANGAL</t>
+          <t>St. THOMAS MOUNT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9528</v>
+        <v>8586</v>
       </c>
       <c r="C14" t="n">
-        <v>2842</v>
+        <v>5212</v>
       </c>
       <c r="D14" t="n">
-        <v>9115</v>
+        <v>8518</v>
       </c>
       <c r="E14" t="n">
-        <v>9966</v>
+        <v>8966</v>
       </c>
       <c r="F14" t="n">
-        <v>10233</v>
+        <v>8853</v>
       </c>
       <c r="G14" t="n">
-        <v>9927</v>
+        <v>8926</v>
       </c>
       <c r="H14" t="n">
-        <v>9562</v>
+        <v>8883</v>
       </c>
       <c r="I14" t="n">
-        <v>5453</v>
+        <v>7919</v>
       </c>
       <c r="J14" t="n">
-        <v>3205</v>
+        <v>5857</v>
       </c>
       <c r="K14" t="n">
-        <v>9154</v>
+        <v>8815</v>
       </c>
       <c r="L14" t="n">
-        <v>9768</v>
+        <v>9041</v>
       </c>
       <c r="M14" t="n">
-        <v>8431</v>
+        <v>7501</v>
       </c>
       <c r="N14" t="n">
-        <v>9345</v>
+        <v>8395</v>
       </c>
       <c r="O14" t="n">
-        <v>9234</v>
+        <v>8449</v>
       </c>
       <c r="P14" t="n">
-        <v>5503</v>
+        <v>7794</v>
       </c>
       <c r="Q14" t="n">
-        <v>3135</v>
+        <v>5501</v>
       </c>
       <c r="R14" t="n">
-        <v>9293</v>
+        <v>8707</v>
       </c>
       <c r="S14" t="n">
-        <v>9796</v>
+        <v>9034</v>
       </c>
       <c r="T14" t="n">
-        <v>10038</v>
+        <v>8666</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9177</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6861</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7330</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASHOK NAGAR</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9566</v>
+        <v>7690</v>
       </c>
       <c r="C15" t="n">
-        <v>4372</v>
+        <v>5729</v>
       </c>
       <c r="D15" t="n">
-        <v>9905</v>
+        <v>8269</v>
       </c>
       <c r="E15" t="n">
-        <v>9740</v>
+        <v>7884</v>
       </c>
       <c r="F15" t="n">
-        <v>10037</v>
+        <v>7720</v>
       </c>
       <c r="G15" t="n">
-        <v>9754</v>
+        <v>7541</v>
       </c>
       <c r="H15" t="n">
-        <v>9921</v>
+        <v>8054</v>
       </c>
       <c r="I15" t="n">
-        <v>8948</v>
+        <v>7847</v>
       </c>
       <c r="J15" t="n">
-        <v>5124</v>
+        <v>6459</v>
       </c>
       <c r="K15" t="n">
-        <v>10057</v>
+        <v>8457</v>
       </c>
       <c r="L15" t="n">
-        <v>10340</v>
+        <v>7747</v>
       </c>
       <c r="M15" t="n">
-        <v>7094</v>
+        <v>6642</v>
       </c>
       <c r="N15" t="n">
-        <v>8605</v>
+        <v>7632</v>
       </c>
       <c r="O15" t="n">
-        <v>9599</v>
+        <v>7795</v>
       </c>
       <c r="P15" t="n">
-        <v>7983</v>
+        <v>7097</v>
       </c>
       <c r="Q15" t="n">
-        <v>5011</v>
+        <v>6083</v>
       </c>
       <c r="R15" t="n">
-        <v>9643</v>
+        <v>8277</v>
       </c>
       <c r="S15" t="n">
-        <v>9788</v>
+        <v>7753</v>
       </c>
       <c r="T15" t="n">
-        <v>9870</v>
+        <v>7542</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7968</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6066</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6878</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AG-DMS</t>
+          <t>TEYNAMPET</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8977</v>
+        <v>10381</v>
       </c>
       <c r="C16" t="n">
-        <v>2324</v>
+        <v>2852</v>
       </c>
       <c r="D16" t="n">
-        <v>9167</v>
+        <v>10642</v>
       </c>
       <c r="E16" t="n">
-        <v>9586</v>
+        <v>10992</v>
       </c>
       <c r="F16" t="n">
-        <v>9582</v>
+        <v>11036</v>
       </c>
       <c r="G16" t="n">
-        <v>10111</v>
+        <v>10957</v>
       </c>
       <c r="H16" t="n">
-        <v>9722</v>
+        <v>10783</v>
       </c>
       <c r="I16" t="n">
-        <v>5668</v>
+        <v>6792</v>
       </c>
       <c r="J16" t="n">
-        <v>2442</v>
+        <v>2889</v>
       </c>
       <c r="K16" t="n">
-        <v>9028</v>
+        <v>10901</v>
       </c>
       <c r="L16" t="n">
-        <v>9177</v>
+        <v>10854</v>
       </c>
       <c r="M16" t="n">
-        <v>5508</v>
+        <v>7659</v>
       </c>
       <c r="N16" t="n">
-        <v>8980</v>
+        <v>10754</v>
       </c>
       <c r="O16" t="n">
-        <v>8784</v>
+        <v>10759</v>
       </c>
       <c r="P16" t="n">
-        <v>5515</v>
+        <v>8192</v>
       </c>
       <c r="Q16" t="n">
-        <v>2536</v>
+        <v>2976</v>
       </c>
       <c r="R16" t="n">
-        <v>8935</v>
+        <v>10442</v>
       </c>
       <c r="S16" t="n">
-        <v>8899</v>
+        <v>10794</v>
       </c>
       <c r="T16" t="n">
-        <v>9220</v>
+        <v>10964</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11021</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7161</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6585</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>St. THOMAS MOUNT</t>
+          <t>WASHERMANPET</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8673</v>
+        <v>8122</v>
       </c>
       <c r="C17" t="n">
-        <v>5212</v>
+        <v>4003</v>
       </c>
       <c r="D17" t="n">
-        <v>8518</v>
+        <v>8476</v>
       </c>
       <c r="E17" t="n">
-        <v>8966</v>
+        <v>8491</v>
       </c>
       <c r="F17" t="n">
-        <v>8853</v>
+        <v>8595</v>
       </c>
       <c r="G17" t="n">
-        <v>8926</v>
+        <v>8636</v>
       </c>
       <c r="H17" t="n">
-        <v>8883</v>
+        <v>8069</v>
       </c>
       <c r="I17" t="n">
-        <v>7919</v>
+        <v>6477</v>
       </c>
       <c r="J17" t="n">
-        <v>5857</v>
+        <v>4493</v>
       </c>
       <c r="K17" t="n">
-        <v>8815</v>
+        <v>8345</v>
       </c>
       <c r="L17" t="n">
-        <v>9041</v>
+        <v>8485</v>
       </c>
       <c r="M17" t="n">
-        <v>7501</v>
+        <v>6228</v>
       </c>
       <c r="N17" t="n">
-        <v>8395</v>
+        <v>8309</v>
       </c>
       <c r="O17" t="n">
-        <v>8449</v>
+        <v>8223</v>
       </c>
       <c r="P17" t="n">
-        <v>7794</v>
+        <v>6570</v>
       </c>
       <c r="Q17" t="n">
-        <v>5501</v>
+        <v>4298</v>
       </c>
       <c r="R17" t="n">
-        <v>8707</v>
+        <v>8462</v>
       </c>
       <c r="S17" t="n">
-        <v>9034</v>
+        <v>8458</v>
       </c>
       <c r="T17" t="n">
-        <v>8666</v>
+        <v>8626</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8645</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5785</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WASHERMANPET</t>
+          <t>ANNA NAGAR EAST</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8262</v>
+        <v>7102</v>
       </c>
       <c r="C18" t="n">
-        <v>4003</v>
+        <v>3712</v>
       </c>
       <c r="D18" t="n">
-        <v>8476</v>
+        <v>7377</v>
       </c>
       <c r="E18" t="n">
-        <v>8491</v>
+        <v>7373</v>
       </c>
       <c r="F18" t="n">
-        <v>8595</v>
+        <v>7471</v>
       </c>
       <c r="G18" t="n">
-        <v>8636</v>
+        <v>7394</v>
       </c>
       <c r="H18" t="n">
-        <v>8069</v>
+        <v>6627</v>
       </c>
       <c r="I18" t="n">
-        <v>6477</v>
+        <v>5956</v>
       </c>
       <c r="J18" t="n">
-        <v>4493</v>
+        <v>4327</v>
       </c>
       <c r="K18" t="n">
-        <v>8345</v>
+        <v>7230</v>
       </c>
       <c r="L18" t="n">
-        <v>8485</v>
+        <v>7311</v>
       </c>
       <c r="M18" t="n">
-        <v>6228</v>
+        <v>5909</v>
       </c>
       <c r="N18" t="n">
-        <v>8309</v>
+        <v>7247</v>
       </c>
       <c r="O18" t="n">
-        <v>8223</v>
+        <v>7195</v>
       </c>
       <c r="P18" t="n">
-        <v>6570</v>
+        <v>6318</v>
       </c>
       <c r="Q18" t="n">
-        <v>4298</v>
+        <v>3889</v>
       </c>
       <c r="R18" t="n">
-        <v>8462</v>
+        <v>7290</v>
       </c>
       <c r="S18" t="n">
-        <v>8458</v>
+        <v>7290</v>
       </c>
       <c r="T18" t="n">
-        <v>8626</v>
+        <v>7282</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8339</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5189</v>
+      </c>
+      <c r="W18" t="n">
+        <v>6387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NANDANAM</t>
+          <t>MEENAMBAKKAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8076</v>
+        <v>7301</v>
       </c>
       <c r="C19" t="n">
-        <v>2019</v>
+        <v>4033</v>
       </c>
       <c r="D19" t="n">
-        <v>7958</v>
+        <v>7855</v>
       </c>
       <c r="E19" t="n">
-        <v>8410</v>
+        <v>7631</v>
       </c>
       <c r="F19" t="n">
-        <v>8460</v>
+        <v>7777</v>
       </c>
       <c r="G19" t="n">
-        <v>8434</v>
+        <v>7746</v>
       </c>
       <c r="H19" t="n">
-        <v>8389</v>
+        <v>7371</v>
       </c>
       <c r="I19" t="n">
-        <v>4552</v>
+        <v>6771</v>
       </c>
       <c r="J19" t="n">
-        <v>2247</v>
+        <v>4767</v>
       </c>
       <c r="K19" t="n">
-        <v>8159</v>
+        <v>7853</v>
       </c>
       <c r="L19" t="n">
-        <v>8542</v>
+        <v>7526</v>
       </c>
       <c r="M19" t="n">
-        <v>5839</v>
+        <v>5227</v>
       </c>
       <c r="N19" t="n">
-        <v>8108</v>
+        <v>7287</v>
       </c>
       <c r="O19" t="n">
-        <v>8038</v>
+        <v>6643</v>
       </c>
       <c r="P19" t="n">
-        <v>6463</v>
+        <v>6093</v>
       </c>
       <c r="Q19" t="n">
-        <v>2108</v>
+        <v>4538</v>
       </c>
       <c r="R19" t="n">
-        <v>7985</v>
+        <v>8060</v>
       </c>
       <c r="S19" t="n">
-        <v>8238</v>
+        <v>7700</v>
       </c>
       <c r="T19" t="n">
-        <v>8426</v>
+        <v>7731</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7633</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5474</v>
+      </c>
+      <c r="W19" t="n">
+        <v>6283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LITTLE MOUNT</t>
+          <t>ANNA NAGAR TOWER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7665</v>
+        <v>6342</v>
       </c>
       <c r="C20" t="n">
-        <v>3363</v>
+        <v>3679</v>
       </c>
       <c r="D20" t="n">
-        <v>7386</v>
+        <v>6366</v>
       </c>
       <c r="E20" t="n">
-        <v>7725</v>
+        <v>6571</v>
       </c>
       <c r="F20" t="n">
-        <v>8126</v>
+        <v>6775</v>
       </c>
       <c r="G20" t="n">
-        <v>7874</v>
+        <v>6937</v>
       </c>
       <c r="H20" t="n">
-        <v>8085</v>
+        <v>6129</v>
       </c>
       <c r="I20" t="n">
-        <v>5171</v>
+        <v>5839</v>
       </c>
       <c r="J20" t="n">
-        <v>3931</v>
+        <v>3755</v>
       </c>
       <c r="K20" t="n">
-        <v>7690</v>
+        <v>6339</v>
       </c>
       <c r="L20" t="n">
-        <v>7922</v>
+        <v>6548</v>
       </c>
       <c r="M20" t="n">
-        <v>6357</v>
+        <v>5379</v>
       </c>
       <c r="N20" t="n">
-        <v>7724</v>
+        <v>6505</v>
       </c>
       <c r="O20" t="n">
-        <v>7756</v>
+        <v>6366</v>
       </c>
       <c r="P20" t="n">
-        <v>6331</v>
+        <v>6178</v>
       </c>
       <c r="Q20" t="n">
-        <v>3585</v>
+        <v>3905</v>
       </c>
       <c r="R20" t="n">
-        <v>7338</v>
+        <v>6521</v>
       </c>
       <c r="S20" t="n">
-        <v>7657</v>
+        <v>6504</v>
       </c>
       <c r="T20" t="n">
-        <v>8009</v>
+        <v>6691</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6801</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4696</v>
+      </c>
+      <c r="W20" t="n">
+        <v>6155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAIDAPET</t>
+          <t>MANNADI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7372</v>
+        <v>6760</v>
       </c>
       <c r="C21" t="n">
-        <v>3326</v>
+        <v>3456</v>
       </c>
       <c r="D21" t="n">
-        <v>7667</v>
+        <v>6880</v>
       </c>
       <c r="E21" t="n">
-        <v>7656</v>
+        <v>7207</v>
       </c>
       <c r="F21" t="n">
-        <v>7918</v>
+        <v>7182</v>
       </c>
       <c r="G21" t="n">
-        <v>7722</v>
+        <v>7153</v>
       </c>
       <c r="H21" t="n">
-        <v>7303</v>
+        <v>6707</v>
       </c>
       <c r="I21" t="n">
-        <v>4748</v>
+        <v>5717</v>
       </c>
       <c r="J21" t="n">
-        <v>3331</v>
+        <v>3630</v>
       </c>
       <c r="K21" t="n">
-        <v>7779</v>
+        <v>6960</v>
       </c>
       <c r="L21" t="n">
-        <v>7675</v>
+        <v>6953</v>
       </c>
       <c r="M21" t="n">
-        <v>4505</v>
+        <v>5284</v>
       </c>
       <c r="N21" t="n">
-        <v>7515</v>
+        <v>6610</v>
       </c>
       <c r="O21" t="n">
-        <v>7231</v>
+        <v>6823</v>
       </c>
       <c r="P21" t="n">
-        <v>5066</v>
+        <v>6099</v>
       </c>
       <c r="Q21" t="n">
-        <v>3095</v>
+        <v>3646</v>
       </c>
       <c r="R21" t="n">
-        <v>7343</v>
+        <v>6945</v>
       </c>
       <c r="S21" t="n">
-        <v>7649</v>
+        <v>6983</v>
       </c>
       <c r="T21" t="n">
-        <v>7874</v>
+        <v>7179</v>
+      </c>
+      <c r="U21" t="n">
+        <v>7397</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5137</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5956</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MEENAMBAKKAM</t>
+          <t>THIYAGARAYA COLLEGE METRO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7416</v>
+        <v>6985</v>
       </c>
       <c r="C22" t="n">
-        <v>4033</v>
+        <v>4309</v>
       </c>
       <c r="D22" t="n">
-        <v>7855</v>
+        <v>7263</v>
       </c>
       <c r="E22" t="n">
-        <v>7631</v>
+        <v>7166</v>
       </c>
       <c r="F22" t="n">
-        <v>7777</v>
+        <v>7273</v>
       </c>
       <c r="G22" t="n">
-        <v>7746</v>
+        <v>7417</v>
       </c>
       <c r="H22" t="n">
-        <v>7371</v>
+        <v>6980</v>
       </c>
       <c r="I22" t="n">
-        <v>6771</v>
+        <v>6253</v>
       </c>
       <c r="J22" t="n">
-        <v>4767</v>
+        <v>5102</v>
       </c>
       <c r="K22" t="n">
-        <v>7853</v>
+        <v>7306</v>
       </c>
       <c r="L22" t="n">
-        <v>7526</v>
+        <v>7308</v>
       </c>
       <c r="M22" t="n">
-        <v>5227</v>
+        <v>5579</v>
       </c>
       <c r="N22" t="n">
-        <v>7287</v>
+        <v>7317</v>
       </c>
       <c r="O22" t="n">
-        <v>6643</v>
+        <v>7071</v>
       </c>
       <c r="P22" t="n">
-        <v>6093</v>
+        <v>6403</v>
       </c>
       <c r="Q22" t="n">
-        <v>4538</v>
+        <v>4725</v>
       </c>
       <c r="R22" t="n">
-        <v>8060</v>
+        <v>7488</v>
       </c>
       <c r="S22" t="n">
-        <v>7700</v>
+        <v>7075</v>
       </c>
       <c r="T22" t="n">
-        <v>7731</v>
+        <v>7340</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7358</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4838</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5862</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>TONDIARPET METRO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7793</v>
+        <v>6818</v>
       </c>
       <c r="C23" t="n">
-        <v>5729</v>
+        <v>3718</v>
       </c>
       <c r="D23" t="n">
-        <v>8269</v>
+        <v>7017</v>
       </c>
       <c r="E23" t="n">
-        <v>7884</v>
+        <v>7052</v>
       </c>
       <c r="F23" t="n">
-        <v>7720</v>
+        <v>7203</v>
       </c>
       <c r="G23" t="n">
-        <v>7541</v>
+        <v>7093</v>
       </c>
       <c r="H23" t="n">
-        <v>8054</v>
+        <v>6735</v>
       </c>
       <c r="I23" t="n">
-        <v>7847</v>
+        <v>6139</v>
       </c>
       <c r="J23" t="n">
-        <v>6459</v>
+        <v>4676</v>
       </c>
       <c r="K23" t="n">
-        <v>8457</v>
+        <v>7079</v>
       </c>
       <c r="L23" t="n">
-        <v>7747</v>
+        <v>7101</v>
       </c>
       <c r="M23" t="n">
-        <v>6642</v>
+        <v>5643</v>
       </c>
       <c r="N23" t="n">
-        <v>7632</v>
+        <v>7036</v>
       </c>
       <c r="O23" t="n">
-        <v>7795</v>
+        <v>6939</v>
       </c>
       <c r="P23" t="n">
-        <v>7097</v>
+        <v>5959</v>
       </c>
       <c r="Q23" t="n">
-        <v>6083</v>
+        <v>4177</v>
       </c>
       <c r="R23" t="n">
-        <v>8277</v>
+        <v>7280</v>
       </c>
       <c r="S23" t="n">
-        <v>7753</v>
+        <v>6937</v>
       </c>
       <c r="T23" t="n">
-        <v>7542</v>
+        <v>7058</v>
+      </c>
+      <c r="U23" t="n">
+        <v>7027</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5072</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5680</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>THIYAGARAYA COLLEGE METRO</t>
+          <t>THIRUVOTRIYUR THERADI METRO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7122</v>
+        <v>6158</v>
       </c>
       <c r="C24" t="n">
-        <v>4309</v>
+        <v>4224</v>
       </c>
       <c r="D24" t="n">
-        <v>7263</v>
+        <v>6165</v>
       </c>
       <c r="E24" t="n">
-        <v>7166</v>
+        <v>6222</v>
       </c>
       <c r="F24" t="n">
-        <v>7273</v>
+        <v>6129</v>
       </c>
       <c r="G24" t="n">
-        <v>7417</v>
+        <v>6332</v>
       </c>
       <c r="H24" t="n">
-        <v>6980</v>
+        <v>6393</v>
       </c>
       <c r="I24" t="n">
-        <v>6253</v>
+        <v>6163</v>
       </c>
       <c r="J24" t="n">
-        <v>5102</v>
+        <v>5396</v>
       </c>
       <c r="K24" t="n">
-        <v>7306</v>
+        <v>6235</v>
       </c>
       <c r="L24" t="n">
-        <v>7308</v>
+        <v>6360</v>
       </c>
       <c r="M24" t="n">
-        <v>5579</v>
+        <v>5283</v>
       </c>
       <c r="N24" t="n">
-        <v>7317</v>
+        <v>6515</v>
       </c>
       <c r="O24" t="n">
-        <v>7071</v>
+        <v>6358</v>
       </c>
       <c r="P24" t="n">
-        <v>6403</v>
+        <v>5852</v>
       </c>
       <c r="Q24" t="n">
-        <v>4725</v>
+        <v>5132</v>
       </c>
       <c r="R24" t="n">
-        <v>7488</v>
+        <v>6614</v>
       </c>
       <c r="S24" t="n">
-        <v>7075</v>
+        <v>6210</v>
       </c>
       <c r="T24" t="n">
-        <v>7340</v>
+        <v>6192</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6372</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4988</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ANNA NAGAR EAST</t>
+          <t>EKKATTUTHANGAL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7154</v>
+        <v>9440</v>
       </c>
       <c r="C25" t="n">
-        <v>3712</v>
+        <v>2842</v>
       </c>
       <c r="D25" t="n">
-        <v>7377</v>
+        <v>9115</v>
       </c>
       <c r="E25" t="n">
-        <v>7373</v>
+        <v>9966</v>
       </c>
       <c r="F25" t="n">
-        <v>7471</v>
+        <v>10233</v>
       </c>
       <c r="G25" t="n">
-        <v>7394</v>
+        <v>9927</v>
       </c>
       <c r="H25" t="n">
-        <v>6627</v>
+        <v>9562</v>
       </c>
       <c r="I25" t="n">
-        <v>5956</v>
+        <v>5453</v>
       </c>
       <c r="J25" t="n">
-        <v>4327</v>
+        <v>3205</v>
       </c>
       <c r="K25" t="n">
-        <v>7230</v>
+        <v>9154</v>
       </c>
       <c r="L25" t="n">
-        <v>7311</v>
+        <v>9768</v>
       </c>
       <c r="M25" t="n">
-        <v>5909</v>
+        <v>8431</v>
       </c>
       <c r="N25" t="n">
-        <v>7247</v>
+        <v>9345</v>
       </c>
       <c r="O25" t="n">
-        <v>7195</v>
+        <v>9234</v>
       </c>
       <c r="P25" t="n">
-        <v>6318</v>
+        <v>5503</v>
       </c>
       <c r="Q25" t="n">
-        <v>3889</v>
+        <v>3135</v>
       </c>
       <c r="R25" t="n">
-        <v>7290</v>
+        <v>9293</v>
       </c>
       <c r="S25" t="n">
-        <v>7290</v>
+        <v>9796</v>
       </c>
       <c r="T25" t="n">
-        <v>7282</v>
+        <v>10038</v>
+      </c>
+      <c r="U25" t="n">
+        <v>9827</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7904</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5534</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANNADI</t>
+          <t>EGMORE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6836</v>
+        <v>5730</v>
       </c>
       <c r="C26" t="n">
-        <v>3456</v>
+        <v>4506</v>
       </c>
       <c r="D26" t="n">
-        <v>6880</v>
+        <v>6004</v>
       </c>
       <c r="E26" t="n">
-        <v>7207</v>
+        <v>5612</v>
       </c>
       <c r="F26" t="n">
-        <v>7182</v>
+        <v>5795</v>
       </c>
       <c r="G26" t="n">
-        <v>7153</v>
+        <v>5521</v>
       </c>
       <c r="H26" t="n">
-        <v>6707</v>
+        <v>5855</v>
       </c>
       <c r="I26" t="n">
-        <v>5717</v>
+        <v>5887</v>
       </c>
       <c r="J26" t="n">
-        <v>3630</v>
+        <v>4644</v>
       </c>
       <c r="K26" t="n">
-        <v>6960</v>
+        <v>5958</v>
       </c>
       <c r="L26" t="n">
-        <v>6953</v>
+        <v>5586</v>
       </c>
       <c r="M26" t="n">
-        <v>5284</v>
+        <v>5042</v>
       </c>
       <c r="N26" t="n">
-        <v>6610</v>
+        <v>5727</v>
       </c>
       <c r="O26" t="n">
-        <v>6823</v>
+        <v>5727</v>
       </c>
       <c r="P26" t="n">
-        <v>6099</v>
+        <v>5600</v>
       </c>
       <c r="Q26" t="n">
-        <v>3646</v>
+        <v>4886</v>
       </c>
       <c r="R26" t="n">
-        <v>6945</v>
+        <v>6169</v>
       </c>
       <c r="S26" t="n">
-        <v>6983</v>
+        <v>6028</v>
       </c>
       <c r="T26" t="n">
-        <v>7179</v>
+        <v>5873</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6156</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4902</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TONDIARPET METRO</t>
+          <t>LITTLE MOUNT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6936</v>
+        <v>7611</v>
       </c>
       <c r="C27" t="n">
-        <v>3718</v>
+        <v>3363</v>
       </c>
       <c r="D27" t="n">
-        <v>7017</v>
+        <v>7386</v>
       </c>
       <c r="E27" t="n">
-        <v>7052</v>
+        <v>7725</v>
       </c>
       <c r="F27" t="n">
-        <v>7203</v>
+        <v>8126</v>
       </c>
       <c r="G27" t="n">
-        <v>7093</v>
+        <v>7874</v>
       </c>
       <c r="H27" t="n">
-        <v>6735</v>
+        <v>8085</v>
       </c>
       <c r="I27" t="n">
+        <v>5171</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3931</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7690</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7922</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6357</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7756</v>
+      </c>
+      <c r="P27" t="n">
+        <v>6331</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3585</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7338</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7657</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8009</v>
+      </c>
+      <c r="U27" t="n">
+        <v>8382</v>
+      </c>
+      <c r="V27" t="n">
         <v>6139</v>
       </c>
-      <c r="J27" t="n">
-        <v>4676</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7079</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7101</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5643</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7036</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6939</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5959</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4177</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7280</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6937</v>
-      </c>
-      <c r="T27" t="n">
-        <v>7058</v>
+      <c r="W27" t="n">
+        <v>5290</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ANNA NAGAR TOWER</t>
+          <t>AG-DMS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6433</v>
+        <v>8784</v>
       </c>
       <c r="C28" t="n">
-        <v>3679</v>
+        <v>2324</v>
       </c>
       <c r="D28" t="n">
-        <v>6366</v>
+        <v>9167</v>
       </c>
       <c r="E28" t="n">
-        <v>6571</v>
+        <v>9586</v>
       </c>
       <c r="F28" t="n">
-        <v>6775</v>
+        <v>9582</v>
       </c>
       <c r="G28" t="n">
-        <v>6937</v>
+        <v>10111</v>
       </c>
       <c r="H28" t="n">
-        <v>6129</v>
+        <v>9722</v>
       </c>
       <c r="I28" t="n">
-        <v>5839</v>
+        <v>5668</v>
       </c>
       <c r="J28" t="n">
-        <v>3755</v>
+        <v>2442</v>
       </c>
       <c r="K28" t="n">
-        <v>6339</v>
+        <v>9028</v>
       </c>
       <c r="L28" t="n">
-        <v>6548</v>
+        <v>9177</v>
       </c>
       <c r="M28" t="n">
-        <v>5379</v>
+        <v>5508</v>
       </c>
       <c r="N28" t="n">
-        <v>6505</v>
+        <v>8980</v>
       </c>
       <c r="O28" t="n">
-        <v>6366</v>
+        <v>8784</v>
       </c>
       <c r="P28" t="n">
-        <v>6178</v>
+        <v>5515</v>
       </c>
       <c r="Q28" t="n">
-        <v>3905</v>
+        <v>2536</v>
       </c>
       <c r="R28" t="n">
-        <v>6521</v>
+        <v>8935</v>
       </c>
       <c r="S28" t="n">
-        <v>6504</v>
+        <v>8899</v>
       </c>
       <c r="T28" t="n">
-        <v>6691</v>
+        <v>9220</v>
+      </c>
+      <c r="U28" t="n">
+        <v>9500</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5566</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>THIRUVOTRIYUR THERADI METRO</t>
+          <t>ARUMBAKKAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6231</v>
+        <v>5231</v>
       </c>
       <c r="C29" t="n">
-        <v>4224</v>
+        <v>2952</v>
       </c>
       <c r="D29" t="n">
-        <v>6165</v>
+        <v>5072</v>
       </c>
       <c r="E29" t="n">
-        <v>6222</v>
+        <v>5229</v>
       </c>
       <c r="F29" t="n">
-        <v>6129</v>
+        <v>5474</v>
       </c>
       <c r="G29" t="n">
-        <v>6332</v>
+        <v>5294</v>
       </c>
       <c r="H29" t="n">
-        <v>6393</v>
+        <v>5569</v>
       </c>
       <c r="I29" t="n">
-        <v>6163</v>
+        <v>5066</v>
       </c>
       <c r="J29" t="n">
-        <v>5396</v>
+        <v>3710</v>
       </c>
       <c r="K29" t="n">
-        <v>6235</v>
+        <v>5257</v>
       </c>
       <c r="L29" t="n">
-        <v>6360</v>
+        <v>5345</v>
       </c>
       <c r="M29" t="n">
-        <v>5283</v>
+        <v>5074</v>
       </c>
       <c r="N29" t="n">
-        <v>6515</v>
+        <v>5132</v>
       </c>
       <c r="O29" t="n">
-        <v>6358</v>
+        <v>5064</v>
       </c>
       <c r="P29" t="n">
-        <v>5852</v>
+        <v>4873</v>
       </c>
       <c r="Q29" t="n">
-        <v>5132</v>
+        <v>3361</v>
       </c>
       <c r="R29" t="n">
-        <v>6614</v>
+        <v>5197</v>
       </c>
       <c r="S29" t="n">
-        <v>6210</v>
+        <v>5468</v>
       </c>
       <c r="T29" t="n">
-        <v>6192</v>
+        <v>5390</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5426</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4468</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5029</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EGMORE</t>
+          <t>WIMCO NAGAR METRO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5761</v>
+        <v>5685</v>
       </c>
       <c r="C30" t="n">
-        <v>4506</v>
+        <v>2965</v>
       </c>
       <c r="D30" t="n">
-        <v>6004</v>
+        <v>6042</v>
       </c>
       <c r="E30" t="n">
-        <v>5612</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="n">
-        <v>5795</v>
+        <v>5902</v>
       </c>
       <c r="G30" t="n">
-        <v>5521</v>
+        <v>5827</v>
       </c>
       <c r="H30" t="n">
-        <v>5855</v>
+        <v>5717</v>
       </c>
       <c r="I30" t="n">
-        <v>5887</v>
+        <v>5073</v>
       </c>
       <c r="J30" t="n">
-        <v>4644</v>
+        <v>3349</v>
       </c>
       <c r="K30" t="n">
-        <v>5958</v>
+        <v>5954</v>
       </c>
       <c r="L30" t="n">
-        <v>5586</v>
+        <v>5917</v>
       </c>
       <c r="M30" t="n">
-        <v>5042</v>
+        <v>4645</v>
       </c>
       <c r="N30" t="n">
-        <v>5727</v>
+        <v>5758</v>
       </c>
       <c r="O30" t="n">
-        <v>5727</v>
+        <v>5899</v>
       </c>
       <c r="P30" t="n">
-        <v>5600</v>
+        <v>5118</v>
       </c>
       <c r="Q30" t="n">
-        <v>4886</v>
+        <v>3303</v>
       </c>
       <c r="R30" t="n">
-        <v>6169</v>
+        <v>5915</v>
       </c>
       <c r="S30" t="n">
-        <v>6028</v>
+        <v>5721</v>
       </c>
       <c r="T30" t="n">
-        <v>5873</v>
+        <v>5836</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5915</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4484</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4765</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WIMCO NAGAR METRO</t>
+          <t>WIMCO NAGAR DEPOT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5760</v>
+        <v>5481</v>
       </c>
       <c r="C31" t="n">
-        <v>2965</v>
+        <v>3183</v>
       </c>
       <c r="D31" t="n">
-        <v>6042</v>
+        <v>5587</v>
       </c>
       <c r="E31" t="n">
-        <v>5747</v>
+        <v>5683</v>
       </c>
       <c r="F31" t="n">
-        <v>5902</v>
+        <v>5744</v>
       </c>
       <c r="G31" t="n">
-        <v>5827</v>
+        <v>5658</v>
       </c>
       <c r="H31" t="n">
-        <v>5717</v>
+        <v>5514</v>
       </c>
       <c r="I31" t="n">
-        <v>5073</v>
+        <v>4765</v>
       </c>
       <c r="J31" t="n">
-        <v>3349</v>
+        <v>3818</v>
       </c>
       <c r="K31" t="n">
-        <v>5954</v>
+        <v>5737</v>
       </c>
       <c r="L31" t="n">
-        <v>5917</v>
+        <v>5714</v>
       </c>
       <c r="M31" t="n">
-        <v>4645</v>
+        <v>4573</v>
       </c>
       <c r="N31" t="n">
-        <v>5758</v>
+        <v>5708</v>
       </c>
       <c r="O31" t="n">
-        <v>5899</v>
+        <v>5579</v>
       </c>
       <c r="P31" t="n">
-        <v>5118</v>
+        <v>4826</v>
       </c>
       <c r="Q31" t="n">
-        <v>3303</v>
+        <v>3254</v>
       </c>
       <c r="R31" t="n">
-        <v>5915</v>
+        <v>5537</v>
       </c>
       <c r="S31" t="n">
-        <v>5721</v>
+        <v>5687</v>
       </c>
       <c r="T31" t="n">
-        <v>5836</v>
+        <v>5714</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5584</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4189</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WIMCO NAGAR DEPOT</t>
+          <t>SAIDAPET</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5572</v>
+        <v>7202</v>
       </c>
       <c r="C32" t="n">
-        <v>3183</v>
+        <v>3326</v>
       </c>
       <c r="D32" t="n">
-        <v>5587</v>
+        <v>7667</v>
       </c>
       <c r="E32" t="n">
-        <v>5683</v>
+        <v>7656</v>
       </c>
       <c r="F32" t="n">
-        <v>5744</v>
+        <v>7918</v>
       </c>
       <c r="G32" t="n">
-        <v>5658</v>
+        <v>7722</v>
       </c>
       <c r="H32" t="n">
-        <v>5514</v>
+        <v>7303</v>
       </c>
       <c r="I32" t="n">
-        <v>4765</v>
+        <v>4748</v>
       </c>
       <c r="J32" t="n">
-        <v>3818</v>
+        <v>3331</v>
       </c>
       <c r="K32" t="n">
-        <v>5737</v>
+        <v>7779</v>
       </c>
       <c r="L32" t="n">
-        <v>5714</v>
+        <v>7675</v>
       </c>
       <c r="M32" t="n">
-        <v>4573</v>
+        <v>4505</v>
       </c>
       <c r="N32" t="n">
-        <v>5708</v>
+        <v>7515</v>
       </c>
       <c r="O32" t="n">
-        <v>5579</v>
+        <v>7231</v>
       </c>
       <c r="P32" t="n">
-        <v>4826</v>
+        <v>5066</v>
       </c>
       <c r="Q32" t="n">
-        <v>3254</v>
+        <v>3095</v>
       </c>
       <c r="R32" t="n">
-        <v>5537</v>
+        <v>7343</v>
       </c>
       <c r="S32" t="n">
-        <v>5687</v>
+        <v>7649</v>
       </c>
       <c r="T32" t="n">
-        <v>5714</v>
+        <v>7874</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7912</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4281</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4508</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KALADIPET METRO</t>
+          <t>NANDANAM</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5380</v>
+        <v>7921</v>
       </c>
       <c r="C33" t="n">
-        <v>3260</v>
+        <v>2019</v>
       </c>
       <c r="D33" t="n">
-        <v>5512</v>
+        <v>7958</v>
       </c>
       <c r="E33" t="n">
-        <v>5397</v>
+        <v>8410</v>
       </c>
       <c r="F33" t="n">
-        <v>5522</v>
+        <v>8460</v>
       </c>
       <c r="G33" t="n">
-        <v>5472</v>
+        <v>8434</v>
       </c>
       <c r="H33" t="n">
-        <v>5327</v>
+        <v>8389</v>
       </c>
       <c r="I33" t="n">
-        <v>4889</v>
+        <v>4552</v>
       </c>
       <c r="J33" t="n">
-        <v>3959</v>
+        <v>2247</v>
       </c>
       <c r="K33" t="n">
-        <v>5471</v>
+        <v>8159</v>
       </c>
       <c r="L33" t="n">
-        <v>5373</v>
+        <v>8542</v>
       </c>
       <c r="M33" t="n">
-        <v>4267</v>
+        <v>5839</v>
       </c>
       <c r="N33" t="n">
-        <v>5443</v>
+        <v>8108</v>
       </c>
       <c r="O33" t="n">
-        <v>5373</v>
+        <v>8038</v>
       </c>
       <c r="P33" t="n">
-        <v>4864</v>
+        <v>6463</v>
       </c>
       <c r="Q33" t="n">
-        <v>3384</v>
+        <v>2108</v>
       </c>
       <c r="R33" t="n">
-        <v>5666</v>
+        <v>7985</v>
       </c>
       <c r="S33" t="n">
-        <v>5489</v>
+        <v>8238</v>
       </c>
       <c r="T33" t="n">
-        <v>5634</v>
+        <v>8426</v>
+      </c>
+      <c r="U33" t="n">
+        <v>8485</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5351</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4476</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARUMBAKKAM</t>
+          <t>KALADIPET METRO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="C34" t="n">
-        <v>2952</v>
+        <v>3260</v>
       </c>
       <c r="D34" t="n">
-        <v>5072</v>
+        <v>5512</v>
       </c>
       <c r="E34" t="n">
-        <v>5229</v>
+        <v>5397</v>
       </c>
       <c r="F34" t="n">
-        <v>5474</v>
+        <v>5522</v>
       </c>
       <c r="G34" t="n">
-        <v>5294</v>
+        <v>5472</v>
       </c>
       <c r="H34" t="n">
-        <v>5569</v>
+        <v>5327</v>
       </c>
       <c r="I34" t="n">
-        <v>5066</v>
+        <v>4889</v>
       </c>
       <c r="J34" t="n">
-        <v>3710</v>
+        <v>3959</v>
       </c>
       <c r="K34" t="n">
-        <v>5257</v>
+        <v>5471</v>
       </c>
       <c r="L34" t="n">
-        <v>5345</v>
+        <v>5373</v>
       </c>
       <c r="M34" t="n">
-        <v>5074</v>
+        <v>4267</v>
       </c>
       <c r="N34" t="n">
-        <v>5132</v>
+        <v>5443</v>
       </c>
       <c r="O34" t="n">
-        <v>5064</v>
+        <v>5373</v>
       </c>
       <c r="P34" t="n">
-        <v>4873</v>
+        <v>4864</v>
       </c>
       <c r="Q34" t="n">
-        <v>3361</v>
+        <v>3384</v>
       </c>
       <c r="R34" t="n">
-        <v>5197</v>
+        <v>5666</v>
       </c>
       <c r="S34" t="n">
-        <v>5468</v>
+        <v>5489</v>
       </c>
       <c r="T34" t="n">
-        <v>5390</v>
+        <v>5634</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5360</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3824</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4402</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>THIRUVOTRIYUR METRO</t>
+          <t>NEW WASHERMENPET METRO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4912</v>
+        <v>4953</v>
       </c>
       <c r="C35" t="n">
-        <v>3087</v>
+        <v>2783</v>
       </c>
       <c r="D35" t="n">
-        <v>5015</v>
+        <v>5198</v>
       </c>
       <c r="E35" t="n">
-        <v>5086</v>
+        <v>5282</v>
       </c>
       <c r="F35" t="n">
-        <v>5029</v>
+        <v>5346</v>
       </c>
       <c r="G35" t="n">
-        <v>4866</v>
+        <v>5093</v>
       </c>
       <c r="H35" t="n">
-        <v>4663</v>
+        <v>5059</v>
       </c>
       <c r="I35" t="n">
-        <v>4269</v>
+        <v>4387</v>
       </c>
       <c r="J35" t="n">
-        <v>3645</v>
+        <v>3409</v>
       </c>
       <c r="K35" t="n">
-        <v>5158</v>
+        <v>5173</v>
       </c>
       <c r="L35" t="n">
-        <v>4915</v>
+        <v>5104</v>
       </c>
       <c r="M35" t="n">
-        <v>4016</v>
+        <v>3970</v>
       </c>
       <c r="N35" t="n">
-        <v>4863</v>
+        <v>4892</v>
       </c>
       <c r="O35" t="n">
-        <v>5084</v>
+        <v>4951</v>
       </c>
       <c r="P35" t="n">
-        <v>4797</v>
+        <v>4333</v>
       </c>
       <c r="Q35" t="n">
-        <v>3386</v>
+        <v>3206</v>
       </c>
       <c r="R35" t="n">
-        <v>5129</v>
+        <v>5419</v>
       </c>
       <c r="S35" t="n">
-        <v>4919</v>
+        <v>5012</v>
       </c>
       <c r="T35" t="n">
-        <v>5114</v>
+        <v>5089</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3706</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEW WASHERMENPET METRO</t>
+          <t>THIRUVOTRIYUR METRO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5045</v>
+        <v>4834</v>
       </c>
       <c r="C36" t="n">
-        <v>2783</v>
+        <v>3087</v>
       </c>
       <c r="D36" t="n">
-        <v>5198</v>
+        <v>5015</v>
       </c>
       <c r="E36" t="n">
-        <v>5282</v>
+        <v>5086</v>
       </c>
       <c r="F36" t="n">
-        <v>5346</v>
+        <v>5029</v>
       </c>
       <c r="G36" t="n">
-        <v>5093</v>
+        <v>4866</v>
       </c>
       <c r="H36" t="n">
-        <v>5059</v>
+        <v>4663</v>
       </c>
       <c r="I36" t="n">
-        <v>4387</v>
+        <v>4269</v>
       </c>
       <c r="J36" t="n">
-        <v>3409</v>
+        <v>3645</v>
       </c>
       <c r="K36" t="n">
-        <v>5173</v>
+        <v>5158</v>
       </c>
       <c r="L36" t="n">
-        <v>5104</v>
+        <v>4915</v>
       </c>
       <c r="M36" t="n">
-        <v>3970</v>
+        <v>4016</v>
       </c>
       <c r="N36" t="n">
-        <v>4892</v>
+        <v>4863</v>
       </c>
       <c r="O36" t="n">
-        <v>4951</v>
+        <v>5084</v>
       </c>
       <c r="P36" t="n">
-        <v>4333</v>
+        <v>4797</v>
       </c>
       <c r="Q36" t="n">
-        <v>3206</v>
+        <v>3386</v>
       </c>
       <c r="R36" t="n">
-        <v>5419</v>
+        <v>5129</v>
       </c>
       <c r="S36" t="n">
-        <v>5012</v>
+        <v>4919</v>
       </c>
       <c r="T36" t="n">
-        <v>5089</v>
+        <v>5114</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5039</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3614</v>
+      </c>
+      <c r="W36" t="n">
+        <v>4035</v>
       </c>
     </row>
     <row r="37">
@@ -3254,7 +3650,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3692</v>
+        <v>3643</v>
       </c>
       <c r="C37" t="n">
         <v>1898</v>
@@ -3310,133 +3706,160 @@
       <c r="T37" t="n">
         <v>3943</v>
       </c>
+      <c r="U37" t="n">
+        <v>3876</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2775</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3283</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PACHAIAPPA S COLLEGE</t>
+          <t>NEHRU PARK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3299</v>
+        <v>3082</v>
       </c>
       <c r="C38" t="n">
-        <v>1418</v>
+        <v>1872</v>
       </c>
       <c r="D38" t="n">
-        <v>3438</v>
+        <v>3109</v>
       </c>
       <c r="E38" t="n">
-        <v>3407</v>
+        <v>3079</v>
       </c>
       <c r="F38" t="n">
-        <v>3402</v>
+        <v>3162</v>
       </c>
       <c r="G38" t="n">
-        <v>3366</v>
+        <v>3400</v>
       </c>
       <c r="H38" t="n">
-        <v>2815</v>
+        <v>3234</v>
       </c>
       <c r="I38" t="n">
-        <v>2551</v>
+        <v>3082</v>
       </c>
       <c r="J38" t="n">
-        <v>1724</v>
+        <v>2176</v>
       </c>
       <c r="K38" t="n">
-        <v>3362</v>
+        <v>3259</v>
       </c>
       <c r="L38" t="n">
-        <v>3323</v>
+        <v>3164</v>
       </c>
       <c r="M38" t="n">
-        <v>2348</v>
+        <v>2702</v>
       </c>
       <c r="N38" t="n">
-        <v>3580</v>
+        <v>2933</v>
       </c>
       <c r="O38" t="n">
-        <v>3313</v>
+        <v>3041</v>
       </c>
       <c r="P38" t="n">
-        <v>3306</v>
+        <v>3105</v>
       </c>
       <c r="Q38" t="n">
-        <v>1653</v>
+        <v>1931</v>
       </c>
       <c r="R38" t="n">
-        <v>3428</v>
+        <v>3038</v>
       </c>
       <c r="S38" t="n">
-        <v>3503</v>
+        <v>3051</v>
       </c>
       <c r="T38" t="n">
-        <v>3604</v>
+        <v>3330</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3264</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2459</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2735</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEHRU PARK</t>
+          <t>KILPAUK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3116</v>
+        <v>2861</v>
       </c>
       <c r="C39" t="n">
-        <v>1872</v>
+        <v>1294</v>
       </c>
       <c r="D39" t="n">
-        <v>3109</v>
+        <v>2961</v>
       </c>
       <c r="E39" t="n">
-        <v>3079</v>
+        <v>2947</v>
       </c>
       <c r="F39" t="n">
-        <v>3162</v>
+        <v>3016</v>
       </c>
       <c r="G39" t="n">
-        <v>3400</v>
+        <v>3030</v>
       </c>
       <c r="H39" t="n">
-        <v>3234</v>
+        <v>2860</v>
       </c>
       <c r="I39" t="n">
-        <v>3082</v>
+        <v>2535</v>
       </c>
       <c r="J39" t="n">
-        <v>2176</v>
+        <v>1506</v>
       </c>
       <c r="K39" t="n">
-        <v>3259</v>
+        <v>2983</v>
       </c>
       <c r="L39" t="n">
-        <v>3164</v>
+        <v>3091</v>
       </c>
       <c r="M39" t="n">
-        <v>2702</v>
+        <v>2600</v>
       </c>
       <c r="N39" t="n">
-        <v>2933</v>
+        <v>2848</v>
       </c>
       <c r="O39" t="n">
-        <v>3041</v>
+        <v>2803</v>
       </c>
       <c r="P39" t="n">
-        <v>3105</v>
+        <v>2450</v>
       </c>
       <c r="Q39" t="n">
-        <v>1931</v>
+        <v>1357</v>
       </c>
       <c r="R39" t="n">
-        <v>3038</v>
+        <v>2923</v>
       </c>
       <c r="S39" t="n">
-        <v>3051</v>
+        <v>2821</v>
       </c>
       <c r="T39" t="n">
-        <v>3330</v>
+        <v>2974</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2963</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2101</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2511</v>
       </c>
     </row>
     <row r="40">
@@ -3446,7 +3869,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3118</v>
+        <v>3070</v>
       </c>
       <c r="C40" t="n">
         <v>1095</v>
@@ -3502,69 +3925,87 @@
       <c r="T40" t="n">
         <v>3321</v>
       </c>
+      <c r="U40" t="n">
+        <v>3320</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2191</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2444</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KILPAUK</t>
+          <t>PACHAIAPPA S COLLEGE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2912</v>
+        <v>3245</v>
       </c>
       <c r="C41" t="n">
-        <v>1294</v>
+        <v>1418</v>
       </c>
       <c r="D41" t="n">
-        <v>2961</v>
+        <v>3438</v>
       </c>
       <c r="E41" t="n">
-        <v>2947</v>
+        <v>3407</v>
       </c>
       <c r="F41" t="n">
-        <v>3016</v>
+        <v>3402</v>
       </c>
       <c r="G41" t="n">
-        <v>3030</v>
+        <v>3366</v>
       </c>
       <c r="H41" t="n">
-        <v>2860</v>
+        <v>2815</v>
       </c>
       <c r="I41" t="n">
-        <v>2535</v>
+        <v>2551</v>
       </c>
       <c r="J41" t="n">
-        <v>1506</v>
+        <v>1724</v>
       </c>
       <c r="K41" t="n">
-        <v>2983</v>
+        <v>3362</v>
       </c>
       <c r="L41" t="n">
-        <v>3091</v>
+        <v>3323</v>
       </c>
       <c r="M41" t="n">
-        <v>2600</v>
+        <v>2348</v>
       </c>
       <c r="N41" t="n">
-        <v>2848</v>
+        <v>3580</v>
       </c>
       <c r="O41" t="n">
-        <v>2803</v>
+        <v>3313</v>
       </c>
       <c r="P41" t="n">
-        <v>2450</v>
+        <v>3306</v>
       </c>
       <c r="Q41" t="n">
-        <v>1357</v>
+        <v>1653</v>
       </c>
       <c r="R41" t="n">
-        <v>2923</v>
+        <v>3428</v>
       </c>
       <c r="S41" t="n">
-        <v>2821</v>
+        <v>3503</v>
       </c>
       <c r="T41" t="n">
-        <v>2974</v>
+        <v>3604</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3557</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2223</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2405</v>
       </c>
     </row>
     <row r="42">
@@ -3574,7 +4015,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2730</v>
+        <v>2689</v>
       </c>
       <c r="C42" t="n">
         <v>1829</v>
@@ -3629,6 +4070,15 @@
       </c>
       <c r="T42" t="n">
         <v>2828</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2858</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1985</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2175</v>
       </c>
     </row>
   </sheetData>
@@ -3716,19 +4166,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31316.46153846154</v>
+        <v>30997.8</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>1969.324783412858</v>
+        <v>2471.846568285107</v>
       </c>
       <c r="E2" t="n">
-        <v>24397.2</v>
+        <v>24894.16666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7790535329170699</v>
+        <v>0.8030946282209276</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3756,19 +4206,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19134.46153846154</v>
+        <v>19027.73333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>743.5858631640575</v>
+        <v>915.6883021348845</v>
       </c>
       <c r="E3" t="n">
-        <v>16896.6</v>
+        <v>17106.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8830454918230497</v>
+        <v>0.8990298371499845</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3796,19 +4246,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18693.53846153846</v>
+        <v>18426</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>1546.163726527941</v>
+        <v>2066.804987690628</v>
       </c>
       <c r="E4" t="n">
-        <v>7987</v>
+        <v>8792.666666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4272599335023208</v>
+        <v>0.4771880314048988</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3836,19 +4286,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17151.23076923077</v>
+        <v>16944.46666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>841.6801801403099</v>
+        <v>1274.612762857055</v>
       </c>
       <c r="E5" t="n">
-        <v>11656.4</v>
+        <v>12045</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6796246961420126</v>
+        <v>0.7108515267520961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3876,19 +4326,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16985.76923076923</v>
+        <v>16801.8</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>987.1355153376992</v>
+        <v>1313.22222034201</v>
       </c>
       <c r="E6" t="n">
-        <v>11069.4</v>
+        <v>11344.83333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.651686706066164</v>
+        <v>0.6752153539104938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3912,27 +4362,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KOYAMBEDU</t>
+          <t>VADAPALANI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13786.15384615385</v>
+        <v>13619.06666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>957.4617351930958</v>
+        <v>822.8839066414678</v>
       </c>
       <c r="E7" t="n">
-        <v>10520.4</v>
+        <v>13169.83333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7631134917977904</v>
+        <v>0.9670143817980674</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Koyambedu</t>
+          <t>Vadapalani</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3952,27 +4402,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VADAPALANI</t>
+          <t>KOYAMBEDU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13711.76923076923</v>
+        <v>13529.26666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>632.6411771093935</v>
+        <v>1430.410354042637</v>
       </c>
       <c r="E8" t="n">
-        <v>12924.2</v>
+        <v>10597.16666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9425625375169002</v>
+        <v>0.7832772409443232</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Vadapalani</t>
+          <t>Koyambedu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3996,19 +4446,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13544</v>
+        <v>13150.86666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2196.949627703528</v>
+        <v>2596.431475992349</v>
       </c>
       <c r="E9" t="n">
-        <v>6162.8</v>
+        <v>6760.666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4550206733608978</v>
+        <v>0.5140852567384659</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4036,19 +4486,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12841.30769230769</v>
+        <v>12668.26666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>619.9306929831464</v>
+        <v>989.5468996801852</v>
       </c>
       <c r="E10" t="n">
-        <v>8954</v>
+        <v>9159.666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6972810102014533</v>
+        <v>0.7230402475476781</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4076,19 +4526,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11290.53846153846</v>
+        <v>11068.13333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>1212.100423190024</v>
+        <v>1617.555601458424</v>
       </c>
       <c r="E11" t="n">
-        <v>4846.6</v>
+        <v>5375.166666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4292620778459841</v>
+        <v>0.4856434689378516</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4116,19 +4566,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10695.61538461538</v>
+        <v>10538.46666666667</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>658.5507495581412</v>
+        <v>881.0891690456326</v>
       </c>
       <c r="E12" t="n">
-        <v>6985</v>
+        <v>7384.333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.65307135202779</v>
+        <v>0.7007028220424223</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4156,19 +4606,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10579.76923076923</v>
+        <v>10381.26666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>892.0870803763266</v>
+        <v>1220.112727032493</v>
       </c>
       <c r="E13" t="n">
-        <v>4740.2</v>
+        <v>5047.666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>0.448043799123145</v>
+        <v>0.4862283985897675</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4192,27 +4642,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASHOK NAGAR</t>
+          <t>EKKATTUTHANGAL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9565.615384615385</v>
+        <v>9439.533333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>844.1753903920612</v>
+        <v>628.8956155341643</v>
       </c>
       <c r="E14" t="n">
-        <v>6287.6</v>
+        <v>4278.666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6573126502778381</v>
+        <v>0.4532709950350653</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ashok Nagar</t>
+          <t>Ekkattuthangal</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4232,27 +4682,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EKKATTUTHANGAL</t>
+          <t>ASHOK NAGAR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9527.846153846154</v>
+        <v>9430.133333333331</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>493.942784499353</v>
+        <v>1138.248520859173</v>
       </c>
       <c r="E15" t="n">
-        <v>4027.6</v>
+        <v>6506</v>
       </c>
       <c r="F15" t="n">
-        <v>0.422718832248793</v>
+        <v>0.6899160139128467</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ekkattuthangal</t>
+          <t>Ashok Nagar</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4276,19 +4726,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8976.846153846154</v>
+        <v>8784.333333333334</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>1110.356687897621</v>
+        <v>1366.600248095704</v>
       </c>
       <c r="E16" t="n">
-        <v>3697</v>
+        <v>3958.333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.411837290807976</v>
+        <v>0.4506128334534967</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4316,19 +4766,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8673.384615384615</v>
+        <v>8586.133333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>412.1629003322066</v>
+        <v>624.6549752425238</v>
       </c>
       <c r="E17" t="n">
-        <v>6456.6</v>
+        <v>6602.166666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7444152757330117</v>
+        <v>0.7689336294179763</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4356,19 +4806,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8261.76923076923</v>
+        <v>8122.2</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>632.1040465311274</v>
+        <v>877.6480094955084</v>
       </c>
       <c r="E18" t="n">
-        <v>5168.2</v>
+        <v>5393.666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6255560831634126</v>
+        <v>0.6640647443631857</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4396,19 +4846,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8075.846153846154</v>
+        <v>7921.466666666666</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>700.4031988973505</v>
+        <v>968.1157595089156</v>
       </c>
       <c r="E19" t="n">
-        <v>3477.8</v>
+        <v>3644.166666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4306421808622102</v>
+        <v>0.4600368618605982</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4436,19 +4886,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7793.307692307692</v>
+        <v>7689.8</v>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>453.174430106735</v>
+        <v>616.3142982973169</v>
       </c>
       <c r="E20" t="n">
-        <v>6643</v>
+        <v>6682.166666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8523980140751927</v>
+        <v>0.8689649492401189</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4476,19 +4926,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7665.307692307692</v>
+        <v>7611.333333333333</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>459.0452745672959</v>
+        <v>616.9183398921108</v>
       </c>
       <c r="E21" t="n">
-        <v>4476.2</v>
+        <v>4611.833333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>0.583955684452428</v>
+        <v>0.6059166155732679</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4516,19 +4966,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7415.923076923077</v>
+        <v>7300.933333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
-        <v>746.3114253378034</v>
+        <v>857.8884764905274</v>
       </c>
       <c r="E22" t="n">
-        <v>5240.4</v>
+        <v>5414.166666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7066416339062516</v>
+        <v>0.741571853826908</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -4556,19 +5006,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7372.076923076923</v>
+        <v>7202</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>886.9474300034606</v>
+        <v>1160.433724333893</v>
       </c>
       <c r="E23" t="n">
-        <v>3913.2</v>
+        <v>4012.333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5308137775598151</v>
+        <v>0.5571137646949922</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4596,19 +5046,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7153.538461538462</v>
+        <v>7101.6</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>425.9950342794728</v>
+        <v>727.1238644727005</v>
       </c>
       <c r="E24" t="n">
-        <v>4840.4</v>
+        <v>5098.166666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6766441567379241</v>
+        <v>0.7178898651946979</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4636,19 +5086,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7121.769230769231</v>
+        <v>6985.266666666666</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>485.2338188691706</v>
+        <v>747.2489991071695</v>
       </c>
       <c r="E25" t="n">
-        <v>5358.4</v>
+        <v>5442.333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7523973083611462</v>
+        <v>0.7791160442455072</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4676,19 +5126,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6936.384615384615</v>
+        <v>6818.133333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>410.1937628449793</v>
+        <v>614.9040420686638</v>
       </c>
       <c r="E26" t="n">
-        <v>4933.8</v>
+        <v>5058.166666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7112927372938685</v>
+        <v>0.7418697199624531</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4716,19 +5166,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6835.846153846154</v>
+        <v>6760</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>501.3794049343349</v>
+        <v>661.7756417397063</v>
       </c>
       <c r="E27" t="n">
-        <v>4509.6</v>
+        <v>4750.666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6596988724596584</v>
+        <v>0.7027613412228797</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4756,19 +5206,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6433.153846153846</v>
+        <v>6341.866666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>377.373344349652</v>
+        <v>581.6811677821286</v>
       </c>
       <c r="E28" t="n">
-        <v>4671.2</v>
+        <v>4918.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7261135224976385</v>
+        <v>0.775560297704146</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4796,19 +5246,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6231.384615384615</v>
+        <v>6157.866666666667</v>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>317.8156012694412</v>
+        <v>438.8935547270573</v>
       </c>
       <c r="E29" t="n">
-        <v>5353.4</v>
+        <v>5390.833333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>0.859102804661268</v>
+        <v>0.8754384635371557</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4836,19 +5286,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5761.307692307692</v>
+        <v>5730.333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>286.9153140491065</v>
+        <v>365.2440801645361</v>
       </c>
       <c r="E30" t="n">
-        <v>5104.6</v>
+        <v>5160.333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8860141260664647</v>
+        <v>0.900529346751207</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4876,19 +5326,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5760</v>
+        <v>5685.266666666666</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>349.0883364804195</v>
+        <v>465.2784829182052</v>
       </c>
       <c r="E31" t="n">
-        <v>3961.6</v>
+        <v>4095.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6877777777777777</v>
+        <v>0.7203707829594626</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4916,19 +5366,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5380.461538461538</v>
+        <v>5275.333333333333</v>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>348.6231526506847</v>
+        <v>515.1746814246141</v>
       </c>
       <c r="E32" t="n">
-        <v>4071.2</v>
+        <v>4126.333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7566637120064049</v>
+        <v>0.7821938582080121</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4956,19 +5406,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5274.23076923077</v>
+        <v>5230.6</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>167.5480795901853</v>
+        <v>264.7580566695347</v>
       </c>
       <c r="E33" t="n">
-        <v>3992.4</v>
+        <v>4165.166666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7569634653248741</v>
+        <v>0.7963076256388687</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4996,19 +5446,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5045.23076923077</v>
+        <v>4953.333333333333</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D34" t="n">
-        <v>356.290413812046</v>
+        <v>477.4721632374673</v>
       </c>
       <c r="E34" t="n">
-        <v>3623.6</v>
+        <v>3703.166666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7182228456424955</v>
+        <v>0.7476110363391656</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5036,19 +5486,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4912.076923076923</v>
+        <v>4834</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D35" t="n">
-        <v>303.0345034091171</v>
+        <v>440.0999886389455</v>
       </c>
       <c r="E35" t="n">
-        <v>3836.8</v>
+        <v>3869.833333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7810952597209391</v>
+        <v>0.8005447524479382</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5076,19 +5526,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3691.538461538461</v>
+        <v>3642.733333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D36" t="n">
-        <v>248.4007566361985</v>
+        <v>335.811908804971</v>
       </c>
       <c r="E36" t="n">
-        <v>2546.6</v>
+        <v>2669.333333333333</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6898478849760367</v>
+        <v>0.7327830749803262</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5116,19 +5566,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3299.153846153846</v>
+        <v>3244.6</v>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D37" t="n">
-        <v>343.9626545023568</v>
+        <v>430.9187527000553</v>
       </c>
       <c r="E37" t="n">
-        <v>2130.4</v>
+        <v>2176.166666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6457413322763412</v>
+        <v>0.6707041443218476</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5152,27 +5602,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OTA - NANGANALLUR ROAD</t>
+          <t>NEHRU PARK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3118.307692307692</v>
+        <v>3081.666666666667</v>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D38" t="n">
-        <v>257.8359894116752</v>
+        <v>242.5096954370122</v>
       </c>
       <c r="E38" t="n">
-        <v>1673</v>
+        <v>2483.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5365089545611524</v>
+        <v>0.805895078420768</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nanganallur Road</t>
+          <t>Nehru Park</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5192,27 +5642,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEHRU PARK</t>
+          <t>OTA - NANGANALLUR ROAD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3115.538461538461</v>
+        <v>3069.933333333333</v>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
-        <v>179.6940062924636</v>
+        <v>344.676964016758</v>
       </c>
       <c r="E39" t="n">
-        <v>2433.2</v>
+        <v>1801.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7809885931558935</v>
+        <v>0.5868205607070729</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nehru Park</t>
+          <t>Nanganallur Road</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5236,19 +5686,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2912.076923076923</v>
+        <v>2861.4</v>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>127.0560647499506</v>
+        <v>241.3704325601746</v>
       </c>
       <c r="E40" t="n">
-        <v>1828.4</v>
+        <v>1942.166666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6278680296906781</v>
+        <v>0.678747000302882</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5276,19 +5726,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2729.769230769231</v>
+        <v>2688.666666666667</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>169.8092821599935</v>
+        <v>252.3893439754954</v>
       </c>
       <c r="E41" t="n">
-        <v>2209.8</v>
+        <v>2204</v>
       </c>
       <c r="F41" t="n">
-        <v>0.809518978780962</v>
+        <v>0.8197371683610216</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5320,7 +5770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5341,6 +5791,9 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5434,6 +5887,21 @@
           <t>2026-09-02 Wed</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03 Thu</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 Fri</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 Sat</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5490,6 +5958,15 @@
       <c r="R2" t="n">
         <v>6</v>
       </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5546,6 +6023,15 @@
       <c r="R3" t="n">
         <v>5</v>
       </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5602,6 +6088,15 @@
       <c r="R4" t="n">
         <v>869</v>
       </c>
+      <c r="S4" t="n">
+        <v>941</v>
+      </c>
+      <c r="T4" t="n">
+        <v>871</v>
+      </c>
+      <c r="U4" t="n">
+        <v>882</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5658,6 +6153,15 @@
       <c r="R5" t="n">
         <v>3090</v>
       </c>
+      <c r="S5" t="n">
+        <v>2815</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3303</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3293</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5714,6 +6218,15 @@
       <c r="R6" t="n">
         <v>6134</v>
       </c>
+      <c r="S6" t="n">
+        <v>6131</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6482</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6744</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5770,6 +6283,15 @@
       <c r="R7" t="n">
         <v>14788</v>
       </c>
+      <c r="S7" t="n">
+        <v>14831</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10992</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11025</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5826,6 +6348,15 @@
       <c r="R8" t="n">
         <v>31752</v>
       </c>
+      <c r="S8" t="n">
+        <v>31099</v>
+      </c>
+      <c r="T8" t="n">
+        <v>17451</v>
+      </c>
+      <c r="U8" t="n">
+        <v>18627</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5882,6 +6413,15 @@
       <c r="R9" t="n">
         <v>47702</v>
       </c>
+      <c r="S9" t="n">
+        <v>46897</v>
+      </c>
+      <c r="T9" t="n">
+        <v>30200</v>
+      </c>
+      <c r="U9" t="n">
+        <v>29063</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5938,6 +6478,15 @@
       <c r="R10" t="n">
         <v>31820</v>
       </c>
+      <c r="S10" t="n">
+        <v>31192</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21348</v>
+      </c>
+      <c r="U10" t="n">
+        <v>20247</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5994,6 +6543,15 @@
       <c r="R11" t="n">
         <v>15896</v>
       </c>
+      <c r="S11" t="n">
+        <v>17274</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13441</v>
+      </c>
+      <c r="U11" t="n">
+        <v>15116</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6050,6 +6608,15 @@
       <c r="R12" t="n">
         <v>14533</v>
       </c>
+      <c r="S12" t="n">
+        <v>15387</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12039</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14434</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6106,6 +6673,15 @@
       <c r="R13" t="n">
         <v>18263</v>
       </c>
+      <c r="S13" t="n">
+        <v>19395</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11853</v>
+      </c>
+      <c r="U13" t="n">
+        <v>15921</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6162,6 +6738,15 @@
       <c r="R14" t="n">
         <v>17914</v>
       </c>
+      <c r="S14" t="n">
+        <v>17185</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12974</v>
+      </c>
+      <c r="U14" t="n">
+        <v>21960</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6218,6 +6803,15 @@
       <c r="R15" t="n">
         <v>14503</v>
       </c>
+      <c r="S15" t="n">
+        <v>14711</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13219</v>
+      </c>
+      <c r="U15" t="n">
+        <v>18306</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6274,6 +6868,15 @@
       <c r="R16" t="n">
         <v>16290</v>
       </c>
+      <c r="S16" t="n">
+        <v>17112</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14180</v>
+      </c>
+      <c r="U16" t="n">
+        <v>18026</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6330,6 +6933,15 @@
       <c r="R17" t="n">
         <v>24260</v>
       </c>
+      <c r="S17" t="n">
+        <v>25667</v>
+      </c>
+      <c r="T17" t="n">
+        <v>18879</v>
+      </c>
+      <c r="U17" t="n">
+        <v>21307</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6386,6 +6998,15 @@
       <c r="R18" t="n">
         <v>41385</v>
       </c>
+      <c r="S18" t="n">
+        <v>39532</v>
+      </c>
+      <c r="T18" t="n">
+        <v>27775</v>
+      </c>
+      <c r="U18" t="n">
+        <v>27435</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6442,6 +7063,15 @@
       <c r="R19" t="n">
         <v>38484</v>
       </c>
+      <c r="S19" t="n">
+        <v>39747</v>
+      </c>
+      <c r="T19" t="n">
+        <v>27913</v>
+      </c>
+      <c r="U19" t="n">
+        <v>26692</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6498,6 +7128,15 @@
       <c r="R20" t="n">
         <v>24355</v>
       </c>
+      <c r="S20" t="n">
+        <v>26944</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18474</v>
+      </c>
+      <c r="U20" t="n">
+        <v>20058</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6554,6 +7193,15 @@
       <c r="R21" t="n">
         <v>14035</v>
       </c>
+      <c r="S21" t="n">
+        <v>15849</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12486</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14301</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6610,6 +7258,15 @@
       <c r="R22" t="n">
         <v>6744</v>
       </c>
+      <c r="S22" t="n">
+        <v>7619</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6999</v>
+      </c>
+      <c r="U22" t="n">
+        <v>8137</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6665,6 +7322,15 @@
       </c>
       <c r="R23" t="n">
         <v>1699</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1881</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1669</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2033</v>
       </c>
     </row>
     <row r="24">
@@ -6706,6 +7372,9 @@
         <v>1519</v>
       </c>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6718,7 +7387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6829,955 +7498,1114 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="n">
-        <v>164932</v>
+        <v>42428</v>
       </c>
       <c r="C2" t="n">
-        <v>97374</v>
+        <v>13013</v>
       </c>
       <c r="D2" t="n">
-        <v>1538</v>
+        <v>932</v>
       </c>
       <c r="E2" t="n">
-        <v>2819</v>
+        <v>1368</v>
       </c>
       <c r="F2" t="n">
-        <v>24679</v>
+        <v>13423</v>
       </c>
       <c r="G2" t="n">
-        <v>4187</v>
+        <v>1781</v>
       </c>
       <c r="H2" t="n">
-        <v>6192</v>
+        <v>2958</v>
       </c>
       <c r="I2" t="n">
-        <v>3253</v>
+        <v>1449</v>
       </c>
       <c r="J2" t="n">
-        <v>67558</v>
+        <v>29415</v>
       </c>
       <c r="K2" t="n">
-        <v>400</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>11365</v>
+        <v>3968</v>
       </c>
       <c r="M2" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="N2" t="n">
-        <v>18365</v>
+        <v>5576</v>
       </c>
       <c r="O2" t="n">
-        <v>1955</v>
+        <v>263</v>
       </c>
       <c r="P2" t="n">
-        <v>6523</v>
+        <v>1331</v>
       </c>
       <c r="Q2" t="n">
-        <v>4570</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="n">
-        <v>384527</v>
+        <v>313629</v>
       </c>
       <c r="C3" t="n">
-        <v>218840</v>
+        <v>129016</v>
       </c>
       <c r="D3" t="n">
-        <v>3802</v>
+        <v>5364</v>
       </c>
       <c r="E3" t="n">
-        <v>6868</v>
+        <v>7668</v>
       </c>
       <c r="F3" t="n">
-        <v>64793</v>
+        <v>84107</v>
       </c>
       <c r="G3" t="n">
-        <v>10131</v>
+        <v>10488</v>
       </c>
       <c r="H3" t="n">
-        <v>14687</v>
+        <v>16241</v>
       </c>
       <c r="I3" t="n">
-        <v>7276</v>
+        <v>7696</v>
       </c>
       <c r="J3" t="n">
-        <v>165687</v>
+        <v>184613</v>
       </c>
       <c r="K3" t="n">
-        <v>939</v>
+        <v>1340</v>
       </c>
       <c r="L3" t="n">
-        <v>27572</v>
+        <v>28241</v>
       </c>
       <c r="M3" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N3" t="n">
-        <v>42652</v>
+        <v>39541</v>
       </c>
       <c r="O3" t="n">
-        <v>4877</v>
+        <v>2461</v>
       </c>
       <c r="P3" t="n">
-        <v>13971</v>
+        <v>9780</v>
       </c>
       <c r="Q3" t="n">
-        <v>10601</v>
+        <v>11047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="n">
-        <v>382870</v>
+        <v>282563</v>
       </c>
       <c r="C4" t="n">
-        <v>217852</v>
+        <v>133327</v>
       </c>
       <c r="D4" t="n">
-        <v>3622</v>
+        <v>4022</v>
       </c>
       <c r="E4" t="n">
-        <v>6823</v>
+        <v>6212</v>
       </c>
       <c r="F4" t="n">
-        <v>64392</v>
+        <v>62414</v>
       </c>
       <c r="G4" t="n">
-        <v>10238</v>
+        <v>9602</v>
       </c>
       <c r="H4" t="n">
-        <v>14371</v>
+        <v>13546</v>
       </c>
       <c r="I4" t="n">
-        <v>7911</v>
+        <v>6898</v>
       </c>
       <c r="J4" t="n">
-        <v>165018</v>
+        <v>149236</v>
       </c>
       <c r="K4" t="n">
-        <v>1042</v>
+        <v>1097</v>
       </c>
       <c r="L4" t="n">
-        <v>26933</v>
+        <v>22197</v>
       </c>
       <c r="M4" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="N4" t="n">
-        <v>42556</v>
+        <v>33805</v>
       </c>
       <c r="O4" t="n">
-        <v>4773</v>
+        <v>3126</v>
       </c>
       <c r="P4" t="n">
-        <v>14442</v>
+        <v>10386</v>
       </c>
       <c r="Q4" t="n">
-        <v>10332</v>
+        <v>9611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="n">
-        <v>382217</v>
+        <v>392222</v>
       </c>
       <c r="C5" t="n">
-        <v>207015</v>
+        <v>218244</v>
       </c>
       <c r="D5" t="n">
-        <v>4046</v>
+        <v>3980</v>
       </c>
       <c r="E5" t="n">
-        <v>7353</v>
+        <v>7287</v>
       </c>
       <c r="F5" t="n">
-        <v>71778</v>
+        <v>67524</v>
       </c>
       <c r="G5" t="n">
-        <v>10316</v>
+        <v>10708</v>
       </c>
       <c r="H5" t="n">
-        <v>15562</v>
+        <v>15415</v>
       </c>
       <c r="I5" t="n">
-        <v>8181</v>
+        <v>7984</v>
       </c>
       <c r="J5" t="n">
-        <v>175202</v>
+        <v>173978</v>
       </c>
       <c r="K5" t="n">
-        <v>1048</v>
+        <v>1151</v>
       </c>
       <c r="L5" t="n">
-        <v>27176</v>
+        <v>29775</v>
       </c>
       <c r="M5" t="n">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="N5" t="n">
-        <v>43235</v>
+        <v>45528</v>
       </c>
       <c r="O5" t="n">
-        <v>4166</v>
+        <v>4447</v>
       </c>
       <c r="P5" t="n">
-        <v>14891</v>
+        <v>14428</v>
       </c>
       <c r="Q5" t="n">
-        <v>10565</v>
+        <v>11105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B6" t="n">
-        <v>210739</v>
+        <v>384527</v>
       </c>
       <c r="C6" t="n">
-        <v>58965</v>
+        <v>218840</v>
       </c>
       <c r="D6" t="n">
-        <v>4228</v>
+        <v>3802</v>
       </c>
       <c r="E6" t="n">
-        <v>6769</v>
+        <v>6868</v>
       </c>
       <c r="F6" t="n">
-        <v>72960</v>
+        <v>64793</v>
       </c>
       <c r="G6" t="n">
-        <v>8669</v>
+        <v>10131</v>
       </c>
       <c r="H6" t="n">
-        <v>13884</v>
+        <v>14687</v>
       </c>
       <c r="I6" t="n">
-        <v>6646</v>
+        <v>7276</v>
       </c>
       <c r="J6" t="n">
-        <v>151774</v>
+        <v>165687</v>
       </c>
       <c r="K6" t="n">
-        <v>1184</v>
+        <v>939</v>
       </c>
       <c r="L6" t="n">
-        <v>21353</v>
+        <v>27572</v>
       </c>
       <c r="M6" t="n">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="N6" t="n">
-        <v>28960</v>
+        <v>42652</v>
       </c>
       <c r="O6" t="n">
-        <v>1197</v>
+        <v>4877</v>
       </c>
       <c r="P6" t="n">
-        <v>6316</v>
+        <v>13971</v>
       </c>
       <c r="Q6" t="n">
-        <v>8461</v>
+        <v>10601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B7" t="n">
-        <v>319952</v>
+        <v>382870</v>
       </c>
       <c r="C7" t="n">
-        <v>136163</v>
+        <v>217852</v>
       </c>
       <c r="D7" t="n">
-        <v>5035</v>
+        <v>3622</v>
       </c>
       <c r="E7" t="n">
-        <v>8628</v>
+        <v>6823</v>
       </c>
       <c r="F7" t="n">
-        <v>78142</v>
+        <v>64392</v>
       </c>
       <c r="G7" t="n">
-        <v>11141</v>
+        <v>10238</v>
       </c>
       <c r="H7" t="n">
-        <v>17333</v>
+        <v>14371</v>
       </c>
       <c r="I7" t="n">
-        <v>7832</v>
+        <v>7911</v>
       </c>
       <c r="J7" t="n">
-        <v>183789</v>
+        <v>165018</v>
       </c>
       <c r="K7" t="n">
-        <v>1400</v>
+        <v>1042</v>
       </c>
       <c r="L7" t="n">
-        <v>28659</v>
+        <v>26933</v>
       </c>
       <c r="M7" t="n">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="N7" t="n">
-        <v>41576</v>
+        <v>42556</v>
       </c>
       <c r="O7" t="n">
-        <v>2564</v>
+        <v>4773</v>
       </c>
       <c r="P7" t="n">
-        <v>11347</v>
+        <v>14442</v>
       </c>
       <c r="Q7" t="n">
-        <v>11538</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B8" t="n">
-        <v>374907</v>
+        <v>382217</v>
       </c>
       <c r="C8" t="n">
-        <v>201431</v>
+        <v>207015</v>
       </c>
       <c r="D8" t="n">
-        <v>4411</v>
+        <v>4046</v>
       </c>
       <c r="E8" t="n">
-        <v>7169</v>
+        <v>7353</v>
       </c>
       <c r="F8" t="n">
-        <v>70067</v>
+        <v>71778</v>
       </c>
       <c r="G8" t="n">
-        <v>10461</v>
+        <v>10316</v>
       </c>
       <c r="H8" t="n">
-        <v>15504</v>
+        <v>15562</v>
       </c>
       <c r="I8" t="n">
-        <v>8093</v>
+        <v>8181</v>
       </c>
       <c r="J8" t="n">
-        <v>173476</v>
+        <v>175202</v>
       </c>
       <c r="K8" t="n">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="L8" t="n">
-        <v>26406</v>
+        <v>27176</v>
       </c>
       <c r="M8" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>42950</v>
+        <v>43235</v>
       </c>
       <c r="O8" t="n">
-        <v>3869</v>
+        <v>4166</v>
       </c>
       <c r="P8" t="n">
-        <v>15301</v>
+        <v>14891</v>
       </c>
       <c r="Q8" t="n">
-        <v>10952</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B9" t="n">
-        <v>390924</v>
+        <v>210739</v>
       </c>
       <c r="C9" t="n">
-        <v>205884</v>
+        <v>58965</v>
       </c>
       <c r="D9" t="n">
-        <v>4691</v>
+        <v>4228</v>
       </c>
       <c r="E9" t="n">
-        <v>8066</v>
+        <v>6769</v>
       </c>
       <c r="F9" t="n">
-        <v>85586</v>
+        <v>72960</v>
       </c>
       <c r="G9" t="n">
-        <v>10684</v>
+        <v>8669</v>
       </c>
       <c r="H9" t="n">
-        <v>15082</v>
+        <v>13884</v>
       </c>
       <c r="I9" t="n">
-        <v>8378</v>
+        <v>6646</v>
       </c>
       <c r="J9" t="n">
-        <v>185040</v>
+        <v>151774</v>
       </c>
       <c r="K9" t="n">
-        <v>645</v>
+        <v>1184</v>
       </c>
       <c r="L9" t="n">
-        <v>20970</v>
+        <v>21353</v>
       </c>
       <c r="M9" t="n">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="N9" t="n">
-        <v>38176</v>
+        <v>28960</v>
       </c>
       <c r="O9" t="n">
-        <v>4075</v>
+        <v>1197</v>
       </c>
       <c r="P9" t="n">
-        <v>16394</v>
+        <v>6316</v>
       </c>
       <c r="Q9" t="n">
-        <v>10302</v>
+        <v>8461</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B10" t="n">
-        <v>313528</v>
+        <v>319952</v>
       </c>
       <c r="C10" t="n">
-        <v>139772</v>
+        <v>136163</v>
       </c>
       <c r="D10" t="n">
-        <v>4438</v>
+        <v>5035</v>
       </c>
       <c r="E10" t="n">
-        <v>6710</v>
+        <v>8628</v>
       </c>
       <c r="F10" t="n">
-        <v>79640</v>
+        <v>78142</v>
       </c>
       <c r="G10" t="n">
-        <v>9618</v>
+        <v>11141</v>
       </c>
       <c r="H10" t="n">
-        <v>14275</v>
+        <v>17333</v>
       </c>
       <c r="I10" t="n">
-        <v>7416</v>
+        <v>7832</v>
       </c>
       <c r="J10" t="n">
-        <v>173756</v>
+        <v>183789</v>
       </c>
       <c r="K10" t="n">
-        <v>499</v>
+        <v>1400</v>
       </c>
       <c r="L10" t="n">
-        <v>25487</v>
+        <v>28659</v>
       </c>
       <c r="M10" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="N10" t="n">
-        <v>38973</v>
+        <v>41576</v>
       </c>
       <c r="O10" t="n">
-        <v>2866</v>
+        <v>2564</v>
       </c>
       <c r="P10" t="n">
-        <v>12842</v>
+        <v>11347</v>
       </c>
       <c r="Q10" t="n">
-        <v>9820</v>
+        <v>11538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B11" t="n">
-        <v>393530</v>
+        <v>374907</v>
       </c>
       <c r="C11" t="n">
-        <v>215330</v>
+        <v>201431</v>
       </c>
       <c r="D11" t="n">
-        <v>3860</v>
+        <v>4411</v>
       </c>
       <c r="E11" t="n">
-        <v>6849</v>
+        <v>7169</v>
       </c>
       <c r="F11" t="n">
-        <v>75189</v>
+        <v>70067</v>
       </c>
       <c r="G11" t="n">
-        <v>9886</v>
+        <v>10461</v>
       </c>
       <c r="H11" t="n">
-        <v>15146</v>
+        <v>15504</v>
       </c>
       <c r="I11" t="n">
-        <v>8025</v>
+        <v>8093</v>
       </c>
       <c r="J11" t="n">
-        <v>178200</v>
+        <v>173476</v>
       </c>
       <c r="K11" t="n">
-        <v>739</v>
+        <v>1063</v>
       </c>
       <c r="L11" t="n">
-        <v>26854</v>
+        <v>26406</v>
       </c>
       <c r="M11" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="N11" t="n">
-        <v>44545</v>
+        <v>42950</v>
       </c>
       <c r="O11" t="n">
-        <v>4247</v>
+        <v>3869</v>
       </c>
       <c r="P11" t="n">
-        <v>16811</v>
+        <v>15301</v>
       </c>
       <c r="Q11" t="n">
-        <v>10453</v>
+        <v>10952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B12" t="n">
-        <v>391543</v>
+        <v>390924</v>
       </c>
       <c r="C12" t="n">
-        <v>209551</v>
+        <v>205884</v>
       </c>
       <c r="D12" t="n">
-        <v>5046</v>
+        <v>4691</v>
       </c>
       <c r="E12" t="n">
-        <v>7347</v>
+        <v>8066</v>
       </c>
       <c r="F12" t="n">
-        <v>78886</v>
+        <v>85586</v>
       </c>
       <c r="G12" t="n">
-        <v>10048</v>
+        <v>10684</v>
       </c>
       <c r="H12" t="n">
-        <v>15478</v>
+        <v>15082</v>
       </c>
       <c r="I12" t="n">
-        <v>8347</v>
+        <v>8378</v>
       </c>
       <c r="J12" t="n">
-        <v>181992</v>
+        <v>185040</v>
       </c>
       <c r="K12" t="n">
-        <v>1093</v>
+        <v>645</v>
       </c>
       <c r="L12" t="n">
-        <v>26578</v>
+        <v>20970</v>
       </c>
       <c r="M12" t="n">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="N12" t="n">
-        <v>43006</v>
+        <v>38176</v>
       </c>
       <c r="O12" t="n">
-        <v>4003</v>
+        <v>4075</v>
       </c>
       <c r="P12" t="n">
-        <v>15204</v>
+        <v>16394</v>
       </c>
       <c r="Q12" t="n">
-        <v>9831</v>
+        <v>10302</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B13" t="n">
-        <v>217114</v>
+        <v>313528</v>
       </c>
       <c r="C13" t="n">
-        <v>58822</v>
+        <v>139772</v>
       </c>
       <c r="D13" t="n">
-        <v>5235</v>
+        <v>4438</v>
       </c>
       <c r="E13" t="n">
-        <v>7342</v>
+        <v>6710</v>
       </c>
       <c r="F13" t="n">
-        <v>75913</v>
+        <v>79640</v>
       </c>
       <c r="G13" t="n">
-        <v>8686</v>
+        <v>9618</v>
       </c>
       <c r="H13" t="n">
-        <v>13977</v>
+        <v>14275</v>
       </c>
       <c r="I13" t="n">
-        <v>7252</v>
+        <v>7416</v>
       </c>
       <c r="J13" t="n">
-        <v>158292</v>
+        <v>173756</v>
       </c>
       <c r="K13" t="n">
-        <v>1028</v>
+        <v>499</v>
       </c>
       <c r="L13" t="n">
-        <v>22342</v>
+        <v>25487</v>
       </c>
       <c r="M13" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="N13" t="n">
-        <v>30090</v>
+        <v>38973</v>
       </c>
       <c r="O13" t="n">
-        <v>1086</v>
+        <v>2866</v>
       </c>
       <c r="P13" t="n">
-        <v>6542</v>
+        <v>12842</v>
       </c>
       <c r="Q13" t="n">
-        <v>8711</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B14" t="n">
-        <v>316406</v>
+        <v>393530</v>
       </c>
       <c r="C14" t="n">
-        <v>124632</v>
+        <v>215330</v>
       </c>
       <c r="D14" t="n">
-        <v>5716</v>
+        <v>3860</v>
       </c>
       <c r="E14" t="n">
-        <v>8403</v>
+        <v>6849</v>
       </c>
       <c r="F14" t="n">
-        <v>86961</v>
+        <v>75189</v>
       </c>
       <c r="G14" t="n">
-        <v>10983</v>
+        <v>9886</v>
       </c>
       <c r="H14" t="n">
-        <v>17156</v>
+        <v>15146</v>
       </c>
       <c r="I14" t="n">
-        <v>8701</v>
+        <v>8025</v>
       </c>
       <c r="J14" t="n">
-        <v>191774</v>
+        <v>178200</v>
       </c>
       <c r="K14" t="n">
-        <v>1271</v>
+        <v>739</v>
       </c>
       <c r="L14" t="n">
-        <v>29072</v>
+        <v>26854</v>
       </c>
       <c r="M14" t="n">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="N14" t="n">
-        <v>40994</v>
+        <v>44545</v>
       </c>
       <c r="O14" t="n">
-        <v>2108</v>
+        <v>4247</v>
       </c>
       <c r="P14" t="n">
-        <v>10423</v>
+        <v>16811</v>
       </c>
       <c r="Q14" t="n">
-        <v>10752</v>
+        <v>10453</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B15" t="n">
-        <v>381292</v>
+        <v>391543</v>
       </c>
       <c r="C15" t="n">
-        <v>198771</v>
+        <v>209551</v>
       </c>
       <c r="D15" t="n">
-        <v>5481</v>
+        <v>5046</v>
       </c>
       <c r="E15" t="n">
-        <v>7805</v>
+        <v>7347</v>
       </c>
       <c r="F15" t="n">
-        <v>74795</v>
+        <v>78886</v>
       </c>
       <c r="G15" t="n">
-        <v>10831</v>
+        <v>10048</v>
       </c>
       <c r="H15" t="n">
-        <v>16459</v>
+        <v>15478</v>
       </c>
       <c r="I15" t="n">
-        <v>8819</v>
+        <v>8347</v>
       </c>
       <c r="J15" t="n">
-        <v>182521</v>
+        <v>181992</v>
       </c>
       <c r="K15" t="n">
-        <v>1202</v>
+        <v>1093</v>
       </c>
       <c r="L15" t="n">
-        <v>27567</v>
+        <v>26578</v>
       </c>
       <c r="M15" t="n">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="N15" t="n">
-        <v>43532</v>
+        <v>43006</v>
       </c>
       <c r="O15" t="n">
-        <v>3828</v>
+        <v>4003</v>
       </c>
       <c r="P15" t="n">
-        <v>14590</v>
+        <v>15204</v>
       </c>
       <c r="Q15" t="n">
-        <v>10971</v>
+        <v>9831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B16" t="n">
-        <v>387172</v>
+        <v>217114</v>
       </c>
       <c r="C16" t="n">
-        <v>217252</v>
+        <v>58822</v>
       </c>
       <c r="D16" t="n">
-        <v>5531</v>
+        <v>5235</v>
       </c>
       <c r="E16" t="n">
-        <v>6849</v>
+        <v>7342</v>
       </c>
       <c r="F16" t="n">
-        <v>71140</v>
+        <v>75913</v>
       </c>
       <c r="G16" t="n">
-        <v>9830</v>
+        <v>8686</v>
       </c>
       <c r="H16" t="n">
-        <v>14407</v>
+        <v>13977</v>
       </c>
       <c r="I16" t="n">
-        <v>8176</v>
+        <v>7252</v>
       </c>
       <c r="J16" t="n">
-        <v>169920</v>
+        <v>158292</v>
       </c>
       <c r="K16" t="n">
-        <v>1124</v>
+        <v>1028</v>
       </c>
       <c r="L16" t="n">
-        <v>23675</v>
+        <v>22342</v>
       </c>
       <c r="M16" t="n">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="N16" t="n">
-        <v>39767</v>
+        <v>30090</v>
       </c>
       <c r="O16" t="n">
-        <v>4073</v>
+        <v>1086</v>
       </c>
       <c r="P16" t="n">
-        <v>14837</v>
+        <v>6542</v>
       </c>
       <c r="Q16" t="n">
-        <v>10147</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B17" t="n">
-        <v>391553</v>
+        <v>316406</v>
       </c>
       <c r="C17" t="n">
-        <v>219797</v>
+        <v>124632</v>
       </c>
       <c r="D17" t="n">
-        <v>4933</v>
+        <v>5716</v>
       </c>
       <c r="E17" t="n">
-        <v>7035</v>
+        <v>8403</v>
       </c>
       <c r="F17" t="n">
-        <v>71160</v>
+        <v>86961</v>
       </c>
       <c r="G17" t="n">
-        <v>9746</v>
+        <v>10983</v>
       </c>
       <c r="H17" t="n">
-        <v>14375</v>
+        <v>17156</v>
       </c>
       <c r="I17" t="n">
-        <v>8379</v>
+        <v>8701</v>
       </c>
       <c r="J17" t="n">
-        <v>171756</v>
+        <v>191774</v>
       </c>
       <c r="K17" t="n">
-        <v>1072</v>
+        <v>1271</v>
       </c>
       <c r="L17" t="n">
-        <v>26087</v>
+        <v>29072</v>
       </c>
       <c r="M17" t="n">
-        <v>115</v>
+        <v>228</v>
       </c>
       <c r="N17" t="n">
-        <v>41969</v>
+        <v>40994</v>
       </c>
       <c r="O17" t="n">
-        <v>4222</v>
+        <v>2108</v>
       </c>
       <c r="P17" t="n">
-        <v>14695</v>
+        <v>10423</v>
       </c>
       <c r="Q17" t="n">
-        <v>9937</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="n">
-        <v>390922</v>
+        <v>381292</v>
       </c>
       <c r="C18" t="n">
-        <v>219433</v>
+        <v>198771</v>
       </c>
       <c r="D18" t="n">
-        <v>4811</v>
+        <v>5481</v>
       </c>
       <c r="E18" t="n">
-        <v>6728</v>
+        <v>7805</v>
       </c>
       <c r="F18" t="n">
-        <v>70189</v>
+        <v>74795</v>
       </c>
       <c r="G18" t="n">
-        <v>9647</v>
+        <v>10831</v>
       </c>
       <c r="H18" t="n">
-        <v>14329</v>
+        <v>16459</v>
       </c>
       <c r="I18" t="n">
-        <v>9093</v>
+        <v>8819</v>
       </c>
       <c r="J18" t="n">
-        <v>171489</v>
+        <v>182521</v>
       </c>
       <c r="K18" t="n">
-        <v>1071</v>
+        <v>1202</v>
       </c>
       <c r="L18" t="n">
-        <v>26120</v>
+        <v>27567</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="N18" t="n">
-        <v>42297</v>
+        <v>43532</v>
       </c>
       <c r="O18" t="n">
-        <v>4511</v>
+        <v>3828</v>
       </c>
       <c r="P18" t="n">
-        <v>14986</v>
+        <v>14590</v>
       </c>
       <c r="Q18" t="n">
-        <v>9884</v>
+        <v>10971</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B19" t="n">
+        <v>387172</v>
+      </c>
+      <c r="C19" t="n">
+        <v>217252</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5531</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6849</v>
+      </c>
+      <c r="F19" t="n">
+        <v>71140</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9830</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14407</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8176</v>
+      </c>
+      <c r="J19" t="n">
+        <v>169920</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23675</v>
+      </c>
+      <c r="M19" t="n">
+        <v>131</v>
+      </c>
+      <c r="N19" t="n">
+        <v>39767</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4073</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14837</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10147</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B20" t="n">
+        <v>391553</v>
+      </c>
+      <c r="C20" t="n">
+        <v>219797</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4933</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7035</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71160</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9746</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14375</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8379</v>
+      </c>
+      <c r="J20" t="n">
+        <v>171756</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26087</v>
+      </c>
+      <c r="M20" t="n">
+        <v>115</v>
+      </c>
+      <c r="N20" t="n">
+        <v>41969</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4222</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14695</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9937</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B21" t="n">
+        <v>390922</v>
+      </c>
+      <c r="C21" t="n">
+        <v>219433</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6728</v>
+      </c>
+      <c r="F21" t="n">
+        <v>70189</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9647</v>
+      </c>
+      <c r="H21" t="n">
+        <v>14329</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9093</v>
+      </c>
+      <c r="J21" t="n">
+        <v>171489</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26120</v>
+      </c>
+      <c r="M21" t="n">
+        <v>120</v>
+      </c>
+      <c r="N21" t="n">
+        <v>42297</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4511</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14986</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9884</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
         <v>46251</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B22" t="n">
         <v>393467</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>211337</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D22" t="n">
         <v>5023</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E22" t="n">
         <v>7288</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F22" t="n">
         <v>79173</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G22" t="n">
         <v>10128</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H22" t="n">
         <v>15340</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I22" t="n">
         <v>9645</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J22" t="n">
         <v>182130</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K22" t="n">
         <v>1053</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L22" t="n">
         <v>25444</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M22" t="n">
         <v>168</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N22" t="n">
         <v>41658</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O22" t="n">
         <v>3998</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P22" t="n">
         <v>14993</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q22" t="n">
         <v>9877</v>
       </c>
     </row>
